--- a/results/excel/srd_all_matrices.xlsx
+++ b/results/excel/srd_all_matrices.xlsx
@@ -596,16 +596,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>0.825823202104942</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2698072805139186</v>
+        <v>0.3086606982665018</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1008870728342676</v>
+        <v>-0.2436138815940961</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>0.05507385341102358</v>
       </c>
     </row>
     <row r="13">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2395292583942728</v>
       </c>
       <c r="C13" t="n">
-        <v>1.156316916488223</v>
+        <v>0.7139470911092473</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1615120461142995</v>
+        <v>-0.3475082298407814</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>0.05590348346406185</v>
       </c>
     </row>
     <row r="14">
@@ -634,16 +634,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>-0.1804247730969623</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.3961456102783726</v>
+        <v>-0.192659466125876</v>
       </c>
       <c r="D14" t="n">
-        <v>1.225216665070995</v>
+        <v>1.185345363580635</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>0.1974229617181374</v>
       </c>
     </row>
     <row r="15">
@@ -653,16 +653,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>0.1150723125977476</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.02997858672376874</v>
+        <v>0.170051676750127</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1645916917909634</v>
+        <v>0.4057767478542424</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0.6915997014067773</v>
       </c>
     </row>
     <row r="17">
@@ -701,16 +701,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.3612531022155291</v>
+        <v>0.3160642706611559</v>
       </c>
       <c r="C20" t="n">
-        <v>0.206414263474607</v>
+        <v>0.2019735949899847</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0338683670742824</v>
+        <v>-0.03696870532305789</v>
       </c>
       <c r="E20" t="n">
-        <v>0.04650399164940427</v>
+        <v>0.04417907581910079</v>
       </c>
     </row>
     <row r="21">
@@ -720,16 +720,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2743111582595926</v>
+        <v>0.2958229614483411</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3962390581584022</v>
+        <v>0.3987056689994692</v>
       </c>
       <c r="D21" t="n">
-        <v>0.07361127619729933</v>
+        <v>0.07130978640091529</v>
       </c>
       <c r="E21" t="n">
-        <v>0.05647706444527984</v>
+        <v>0.05488123411186797</v>
       </c>
     </row>
     <row r="22">
@@ -739,16 +739,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2242720165600856</v>
+        <v>0.2502882998712602</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2507661283284331</v>
+        <v>0.2516794185553414</v>
       </c>
       <c r="D22" t="n">
-        <v>0.618391579689255</v>
+        <v>0.620779575051986</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2139961057555683</v>
+        <v>0.2140587036518242</v>
       </c>
     </row>
     <row r="23">
@@ -758,16 +758,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1401637229647925</v>
+        <v>0.1378244680192424</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1465805500385575</v>
+        <v>0.1476413174552046</v>
       </c>
       <c r="D23" t="n">
-        <v>0.341865511187728</v>
+        <v>0.3448793438701563</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6830228381497476</v>
+        <v>0.6868809864172071</v>
       </c>
     </row>
     <row r="25">
@@ -806,16 +806,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>0.825823202104942</v>
       </c>
       <c r="C28" t="n">
-        <v>0.5937363454675456</v>
+        <v>0.6792369524986169</v>
       </c>
       <c r="D28" t="n">
-        <v>1.839203440373532</v>
+        <v>-4.441158580214297</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>11.57112227980977</v>
       </c>
     </row>
     <row r="29">
@@ -825,16 +825,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.3251525444431539</v>
       </c>
       <c r="C29" t="n">
-        <v>1.156316916488223</v>
+        <v>0.7139470911092473</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4060081096456374</v>
+        <v>-0.8735643122501798</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>3.568996824289313</v>
       </c>
     </row>
     <row r="30">
@@ -844,16 +844,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>-0.4111584771723353</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.6322524297857384</v>
+        <v>-0.3074864706785781</v>
       </c>
       <c r="D30" t="n">
-        <v>1.225216665070995</v>
+        <v>1.185345363580635</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>0.7704453350982655</v>
       </c>
     </row>
     <row r="31">
@@ -863,16 +863,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.5655918456373219</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0953078268477885</v>
+        <v>0.5406277458045468</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.2901130267005375</v>
+        <v>0.7152312440788602</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0.6915997014067773</v>
       </c>
     </row>
     <row r="33">
@@ -911,16 +911,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.3612531022155291</v>
+        <v>0.3160642706611559</v>
       </c>
       <c r="C36" t="n">
-        <v>0.4542340377707708</v>
+        <v>0.4444619283137151</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.6174311087921268</v>
+        <v>-0.6739512616053296</v>
       </c>
       <c r="E36" t="n">
-        <v>9.770577879462532</v>
+        <v>9.282108602364113</v>
       </c>
     </row>
     <row r="37">
@@ -930,16 +930,16 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.3723677502914517</v>
+        <v>0.4015692665875052</v>
       </c>
       <c r="C37" t="n">
-        <v>0.3962390581584022</v>
+        <v>0.3987056689994692</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1850436287353949</v>
+        <v>0.1792581561091777</v>
       </c>
       <c r="E37" t="n">
-        <v>3.605615449347906</v>
+        <v>3.503734259856147</v>
       </c>
     </row>
     <row r="38">
@@ -949,16 +949,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5110791562512215</v>
+        <v>0.5703660005370558</v>
       </c>
       <c r="C38" t="n">
-        <v>0.4002252955225286</v>
+        <v>0.4016829160289291</v>
       </c>
       <c r="D38" t="n">
-        <v>0.618391579689255</v>
+        <v>0.620779575051986</v>
       </c>
       <c r="E38" t="n">
-        <v>0.8351222166546284</v>
+        <v>0.8353665056508909</v>
       </c>
     </row>
     <row r="39">
@@ -968,16 +968,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6889186197219691</v>
+        <v>0.6774209493249652</v>
       </c>
       <c r="C39" t="n">
-        <v>0.4660084149748129</v>
+        <v>0.4693808033466577</v>
       </c>
       <c r="D39" t="n">
-        <v>0.6025798574399457</v>
+        <v>0.6078921068734028</v>
       </c>
       <c r="E39" t="n">
-        <v>0.6830228381497476</v>
+        <v>0.6868809864172071</v>
       </c>
     </row>
   </sheetData>
@@ -1135,16 +1135,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.286652131782946</v>
+        <v>0.978403301412867</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>-0.4415946146894145</v>
       </c>
       <c r="D12" t="n">
-        <v>1.681818181818182</v>
+        <v>0.0600976725883197</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>0.03638485820291888</v>
       </c>
     </row>
     <row r="13">
@@ -1154,16 +1154,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.3379441214470285</v>
+        <v>0.2353471690725604</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>1.433414232792462</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.045454545454546</v>
+        <v>0.08942415536968072</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>0.04677274258510936</v>
       </c>
     </row>
     <row r="14">
@@ -1173,16 +1173,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.2444121447028424</v>
+        <v>-0.06939302689522148</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.4890479792261568</v>
       </c>
       <c r="D14" t="n">
-        <v>6.727272727272728</v>
+        <v>0.5981686063566812</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>0.209095125790541</v>
       </c>
     </row>
     <row r="15">
@@ -1192,16 +1192,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.3801841085271318</v>
+        <v>-0.144357443590206</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>-0.4808675973292044</v>
       </c>
       <c r="D15" t="n">
-        <v>-3.363636363636364</v>
+        <v>0.2523095656853182</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0.707747273421431</v>
       </c>
     </row>
     <row r="17">
@@ -1246,7 +1246,7 @@
         <v>0.2104135443483551</v>
       </c>
       <c r="D20" t="n">
-        <v>0.04917938285264353</v>
+        <v>0.05288670728475336</v>
       </c>
       <c r="E20" t="n">
         <v>0.04345033704356417</v>
@@ -1265,7 +1265,7 @@
         <v>0.3524226351489942</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1442719649952489</v>
+        <v>0.1482804631365827</v>
       </c>
       <c r="E21" t="n">
         <v>0.05750677475076646</v>
@@ -1284,7 +1284,7 @@
         <v>0.2869923327553162</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5171517252218948</v>
+        <v>0.5086917416492182</v>
       </c>
       <c r="E22" t="n">
         <v>0.2086633956869678</v>
@@ -1303,7 +1303,7 @@
         <v>0.1501714877473345</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2893969269302126</v>
+        <v>0.2901410879294457</v>
       </c>
       <c r="E23" t="n">
         <v>0.690379492518702</v>
@@ -1345,16 +1345,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.286652131782946</v>
+        <v>0.978403301412867</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>-1.024624987892701</v>
       </c>
       <c r="D28" t="n">
-        <v>17.93072420332227</v>
+        <v>0.6407320387497264</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>6.046576568829624</v>
       </c>
     </row>
     <row r="29">
@@ -1364,16 +1364,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.4479733702562428</v>
+        <v>0.3119724765688114</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>1.433414232792462</v>
       </c>
       <c r="D29" t="n">
-        <v>-8.623104609872046</v>
+        <v>0.1906124114702087</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>2.529036007312774</v>
       </c>
     </row>
     <row r="30">
@@ -1383,16 +1383,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.5335849619560349</v>
+        <v>-0.1514944180082319</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.764539783364749</v>
       </c>
       <c r="D30" t="n">
-        <v>6.727272727272728</v>
+        <v>0.5981686063566812</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>0.8542142945297829</v>
       </c>
     </row>
     <row r="31">
@@ -1402,16 +1402,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-1.781498375072699</v>
+        <v>-0.6764421379470879</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>-1.492818073608225</v>
       </c>
       <c r="D31" t="n">
-        <v>-5.948148672394878</v>
+        <v>0.4461762943189241</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0.707747273421431</v>
       </c>
     </row>
     <row r="33">
@@ -1456,7 +1456,7 @@
         <v>0.4882192131849875</v>
       </c>
       <c r="D36" t="n">
-        <v>0.5243265651148014</v>
+        <v>0.5638522478806607</v>
       </c>
       <c r="E36" t="n">
         <v>7.22074519048939</v>
@@ -1475,7 +1475,7 @@
         <v>0.3524226351489942</v>
       </c>
       <c r="D37" t="n">
-        <v>0.3075234766445869</v>
+        <v>0.3160678066853327</v>
       </c>
       <c r="E37" t="n">
         <v>3.109432886995489</v>
@@ -1494,7 +1494,7 @@
         <v>0.4486616144683536</v>
       </c>
       <c r="D38" t="n">
-        <v>0.5171517252218948</v>
+        <v>0.5086917416492182</v>
       </c>
       <c r="E38" t="n">
         <v>0.8524505517143691</v>
@@ -1513,7 +1513,7 @@
         <v>0.4661963340740201</v>
       </c>
       <c r="D39" t="n">
-        <v>0.5117604165909762</v>
+        <v>0.5130763674789761</v>
       </c>
       <c r="E39" t="n">
         <v>0.690379492518702</v>
@@ -1674,16 +1674,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.641666666666667</v>
+        <v>2.629164791609172</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1.239346282698884</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>0.06892712833843267</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>0.03454479024823974</v>
       </c>
     </row>
     <row r="13">
@@ -1693,16 +1693,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-1.175</v>
+        <v>0.7774502841728175</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0.9151608255654498</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>0.1216467814584219</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>0.04096012334261515</v>
       </c>
     </row>
     <row r="14">
@@ -1712,16 +1712,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-1.475</v>
+        <v>-1.670632808759454</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>-0.8196115190334843</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0.5322748290721897</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>0.2163250963571263</v>
       </c>
     </row>
     <row r="15">
@@ -1731,16 +1731,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.008333333333333333</v>
+        <v>-0.7359822670225354</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>-0.3348955892308493</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>0.2771512611309553</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0.7081699900520195</v>
       </c>
     </row>
     <row r="17">
@@ -1779,13 +1779,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.29753566637282</v>
+        <v>0.2858954163089096</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1952035237988786</v>
+        <v>0.1937124195651734</v>
       </c>
       <c r="D20" t="n">
-        <v>0.03530430882485826</v>
+        <v>0.03460444436003175</v>
       </c>
       <c r="E20" t="n">
         <v>0.03433472835220486</v>
@@ -1798,13 +1798,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2848446246460529</v>
+        <v>0.2911221493875605</v>
       </c>
       <c r="C21" t="n">
-        <v>0.389820402246254</v>
+        <v>0.3915263156621976</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1670346289732514</v>
+        <v>0.166805537027026</v>
       </c>
       <c r="E21" t="n">
         <v>0.04720265115999692</v>
@@ -1817,13 +1817,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2586413752948218</v>
+        <v>0.2628724636102209</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2654664870608077</v>
+        <v>0.2659031023216767</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4903818882762884</v>
+        <v>0.4908814333883475</v>
       </c>
       <c r="E22" t="n">
         <v>0.2191425885070876</v>
@@ -1836,13 +1836,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.158978333686305</v>
+        <v>0.1601099706933089</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1495095868940593</v>
+        <v>0.148858162450952</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3072791739256016</v>
+        <v>0.3077085852245944</v>
       </c>
       <c r="E23" t="n">
         <v>0.699320031980711</v>
@@ -1884,16 +1884,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3.641666666666667</v>
+        <v>2.629164791609172</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>2.713579202020262</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>0.6877779365306262</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>5.409087707488753</v>
       </c>
     </row>
     <row r="29">
@@ -1903,16 +1903,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.557031146580226</v>
+        <v>1.030224942446574</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>0.9151608255654498</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>0.257372827403635</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>2.182045706497137</v>
       </c>
     </row>
     <row r="30">
@@ -1922,16 +1922,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-3.310362570301948</v>
+        <v>-3.749423944973362</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>-1.302509092018563</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0.5322748290721897</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>0.8322418072011599</v>
       </c>
     </row>
     <row r="31">
@@ -1941,16 +1941,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.04052664980014486</v>
+        <v>-3.57922747136868</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>-1.064824490548915</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>0.5011574012679262</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0.7081699900520195</v>
       </c>
     </row>
     <row r="33">
@@ -1989,13 +1989,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.29753566637282</v>
+        <v>0.2858954163089096</v>
       </c>
       <c r="C36" t="n">
-        <v>0.4274029217953462</v>
+        <v>0.4241381123606372</v>
       </c>
       <c r="D36" t="n">
-        <v>0.3522781995933232</v>
+        <v>0.3452947179211135</v>
       </c>
       <c r="E36" t="n">
         <v>5.37619582389389</v>
@@ -2008,13 +2008,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.3774569808594536</v>
+        <v>0.3857755353666497</v>
       </c>
       <c r="C37" t="n">
-        <v>0.389820402246254</v>
+        <v>0.3915263156621976</v>
       </c>
       <c r="D37" t="n">
-        <v>0.3534016619079776</v>
+        <v>0.3529169631660254</v>
       </c>
       <c r="E37" t="n">
         <v>2.514600394081171</v>
@@ -2027,13 +2027,13 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.58047235790332</v>
+        <v>0.5899682469819229</v>
       </c>
       <c r="C38" t="n">
-        <v>0.4218736620864941</v>
+        <v>0.4225675217185141</v>
       </c>
       <c r="D38" t="n">
-        <v>0.4903818882762884</v>
+        <v>0.4908814333883475</v>
       </c>
       <c r="E38" t="n">
         <v>0.8430812095550496</v>
@@ -2046,13 +2046,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7731431106138548</v>
+        <v>0.7786464854159022</v>
       </c>
       <c r="C39" t="n">
-        <v>0.4753764301950989</v>
+        <v>0.4733051795633544</v>
       </c>
       <c r="D39" t="n">
-        <v>0.5556360510138401</v>
+        <v>0.5564125318777557</v>
       </c>
       <c r="E39" t="n">
         <v>0.699320031980711</v>
@@ -2213,16 +2213,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.116883116883117</v>
+        <v>3.711492672382564</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.9320894929689054</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1800554016620499</v>
+        <v>0.04430511706399341</v>
       </c>
       <c r="E12" t="n">
-        <v>0.005604820368918326</v>
+        <v>0.04048839375257306</v>
       </c>
     </row>
     <row r="13">
@@ -2232,16 +2232,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.525974025974026</v>
+        <v>0.5938999668039281</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>1.12894716292007</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1634349030470914</v>
+        <v>0.1283526362682412</v>
       </c>
       <c r="E13" t="n">
-        <v>0.005768108301386604</v>
+        <v>0.0409576473836728</v>
       </c>
     </row>
     <row r="14">
@@ -2251,16 +2251,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.5779220779220779</v>
+        <v>-1.792993868184906</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>-0.7574614624378281</v>
       </c>
       <c r="D14" t="n">
-        <v>1.127423822714681</v>
+        <v>0.5374027665271723</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1874791148188622</v>
+        <v>0.1990226852800379</v>
       </c>
     </row>
     <row r="15">
@@ -2270,16 +2270,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-1.012987012987013</v>
+        <v>-1.512398771001585</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>-0.3035751934511478</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1440443213296399</v>
+        <v>0.289939480140593</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8011479565108328</v>
+        <v>0.7195312735837166</v>
       </c>
     </row>
     <row r="17">
@@ -2318,16 +2318,16 @@
         </is>
       </c>
       <c r="B20" t="n">
+        <v>0.01746723834502813</v>
+      </c>
+      <c r="C20" t="n">
         <v>9.366666666666667</v>
       </c>
-      <c r="C20" t="n">
-        <v>-0.002938110642225071</v>
-      </c>
       <c r="D20" t="n">
-        <v>0.07690313491866135</v>
+        <v>-2.637290977989678e-05</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1466421614786127</v>
+        <v>0.3138301828978291</v>
       </c>
     </row>
     <row r="21">
@@ -2337,16 +2337,16 @@
         </is>
       </c>
       <c r="B21" t="n">
+        <v>0.1545608550904455</v>
+      </c>
+      <c r="C21" t="n">
         <v>-6.4</v>
       </c>
-      <c r="C21" t="n">
-        <v>0.07312336576965732</v>
-      </c>
       <c r="D21" t="n">
-        <v>0.1474714287784663</v>
+        <v>-0.08825671195836493</v>
       </c>
       <c r="E21" t="n">
-        <v>0.07205379290245083</v>
+        <v>0.2729513073186731</v>
       </c>
     </row>
     <row r="22">
@@ -2356,16 +2356,16 @@
         </is>
       </c>
       <c r="B22" t="n">
+        <v>0.5079641102145492</v>
+      </c>
+      <c r="C22" t="n">
         <v>-9.866666666666667</v>
       </c>
-      <c r="C22" t="n">
-        <v>0.3393257561360015</v>
-      </c>
       <c r="D22" t="n">
-        <v>0.4797931309053481</v>
+        <v>0.4485720916575998</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3857612915007774</v>
+        <v>0.2576183851563014</v>
       </c>
     </row>
     <row r="23">
@@ -2375,16 +2375,16 @@
         </is>
       </c>
       <c r="B23" t="n">
+        <v>0.3200077963499771</v>
+      </c>
+      <c r="C23" t="n">
         <v>7.9</v>
       </c>
-      <c r="C23" t="n">
-        <v>0.5904889887365664</v>
-      </c>
       <c r="D23" t="n">
-        <v>0.2958323053975241</v>
+        <v>0.6397109932105453</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3955427541181595</v>
+        <v>0.1556001246271962</v>
       </c>
     </row>
     <row r="25">
@@ -2423,16 +2423,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3.116883116883117</v>
+        <v>3.711492672382564</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>2.141075713489619</v>
       </c>
       <c r="D28" t="n">
-        <v>2.11132516903292</v>
+        <v>0.5195207025764842</v>
       </c>
       <c r="E28" t="n">
-        <v>0.9628367209662072</v>
+        <v>6.955390130627785</v>
       </c>
     </row>
     <row r="29">
@@ -2442,16 +2442,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.705233926282079</v>
+        <v>0.7963100547261891</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>1.12894716292007</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.3683146483248006</v>
+        <v>0.2892537347122049</v>
       </c>
       <c r="E29" t="n">
-        <v>0.3557639148385346</v>
+        <v>2.526175344573349</v>
       </c>
     </row>
     <row r="30">
@@ -2461,16 +2461,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-1.239489365276029</v>
+        <v>-3.845495641230669</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>-1.146679456209752</v>
       </c>
       <c r="D30" t="n">
-        <v>1.127423822714681</v>
+        <v>0.5374027665271723</v>
       </c>
       <c r="E30" t="n">
-        <v>0.7703496789637437</v>
+        <v>0.8177820866079437</v>
       </c>
     </row>
     <row r="31">
@@ -2480,16 +2480,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-4.820145256405067</v>
+        <v>-7.196520457197219</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>-0.9407041175023819</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.2641533536823686</v>
+        <v>0.5317008358058789</v>
       </c>
       <c r="E31" t="n">
-        <v>0.8011479565108328</v>
+        <v>0.7195312735837166</v>
       </c>
     </row>
     <row r="33">
@@ -2528,16 +2528,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>9.366666666666667</v>
+        <v>0.01746723834502813</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.006749048655806856</v>
+        <v>21.51589806304338</v>
       </c>
       <c r="D36" t="n">
-        <v>0.9017642505169355</v>
+        <v>-0.0003092480852279065</v>
       </c>
       <c r="E36" t="n">
-        <v>25.19125478069749</v>
+        <v>53.91202649727132</v>
       </c>
     </row>
     <row r="37">
@@ -2547,16 +2547,16 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-8.581216762266878</v>
+        <v>0.2072375313269426</v>
       </c>
       <c r="C37" t="n">
-        <v>0.07312336576965732</v>
+        <v>-6.4</v>
       </c>
       <c r="D37" t="n">
-        <v>0.3323395824014796</v>
+        <v>-0.1988941114853673</v>
       </c>
       <c r="E37" t="n">
-        <v>4.444115488569917</v>
+        <v>16.83502121980677</v>
       </c>
     </row>
     <row r="38">
@@ -2566,16 +2566,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-21.16137948567135</v>
+        <v>1.089448104866702</v>
       </c>
       <c r="C38" t="n">
-        <v>0.513686692748319</v>
+        <v>-14.93660671728874</v>
       </c>
       <c r="D38" t="n">
-        <v>0.4797931309053481</v>
+        <v>0.4485720916575998</v>
       </c>
       <c r="E38" t="n">
-        <v>1.585089023656755</v>
+        <v>1.058551191112986</v>
       </c>
     </row>
     <row r="39">
@@ -2585,16 +2585,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>37.59095332655388</v>
+        <v>1.522708624901943</v>
       </c>
       <c r="C39" t="n">
-        <v>1.829778700721455</v>
+        <v>24.48013766798348</v>
       </c>
       <c r="D39" t="n">
-        <v>0.5425072982884942</v>
+        <v>1.173123679463462</v>
       </c>
       <c r="E39" t="n">
-        <v>0.3955427541181595</v>
+        <v>0.1556001246271962</v>
       </c>
     </row>
   </sheetData>
@@ -2752,16 +2752,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.802275960170697</v>
+        <v>1.562291156702634</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1490683229813665</v>
+        <v>1.050122093535623</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>0.01873432750490876</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.00354935423958733</v>
+        <v>0.04839909182638197</v>
       </c>
     </row>
     <row r="13">
@@ -2771,16 +2771,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1891891891891892</v>
+        <v>0.5217655096675606</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9316770186335404</v>
+        <v>3.045241197469053</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>0.1630850235964748</v>
       </c>
       <c r="E13" t="n">
-        <v>0.005094428367873281</v>
+        <v>0.05382421796092282</v>
       </c>
     </row>
     <row r="14">
@@ -2790,16 +2790,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.05263157894736842</v>
+        <v>-0.7396776453747576</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.1149068322981366</v>
+        <v>0.07012808459566471</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0.5746237211426026</v>
       </c>
       <c r="E14" t="n">
-        <v>0.193875322696608</v>
+        <v>0.1848565134705197</v>
       </c>
     </row>
     <row r="15">
@@ -2809,16 +2809,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.04409672830725463</v>
+        <v>-0.3443790209954373</v>
       </c>
       <c r="C15" t="n">
-        <v>0.03416149068322982</v>
+        <v>-3.165491375600341</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>0.2435569277560138</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8045796031751061</v>
+        <v>0.7129201767421751</v>
       </c>
     </row>
     <row r="17">
@@ -2857,16 +2857,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.28924040832123</v>
+        <v>0.2893266001796041</v>
       </c>
       <c r="C20" t="n">
         <v>0.1848502193123929</v>
       </c>
       <c r="D20" t="n">
-        <v>0.03464904876713126</v>
+        <v>0.03450268410856393</v>
       </c>
       <c r="E20" t="n">
-        <v>0.03490529958979646</v>
+        <v>0.03548207712513024</v>
       </c>
     </row>
     <row r="21">
@@ -2876,16 +2876,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.3366841062152798</v>
+        <v>0.3355709632733569</v>
       </c>
       <c r="C21" t="n">
         <v>0.3940320797542462</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1713881851974819</v>
+        <v>0.1710169367493606</v>
       </c>
       <c r="E21" t="n">
-        <v>0.05070455078086816</v>
+        <v>0.05090927268588474</v>
       </c>
     </row>
     <row r="22">
@@ -2895,16 +2895,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2247748671187143</v>
+        <v>0.226385023889188</v>
       </c>
       <c r="C22" t="n">
         <v>0.2652771264652093</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4736382371392849</v>
+        <v>0.4730798942757271</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1995958453995003</v>
+        <v>0.1990848669304988</v>
       </c>
     </row>
     <row r="23">
@@ -2914,16 +2914,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1493006183447759</v>
+        <v>0.148717412657851</v>
       </c>
       <c r="C23" t="n">
         <v>0.1558405744681509</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3203245288961021</v>
+        <v>0.3214004848663486</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7147943042298349</v>
+        <v>0.7145237832584861</v>
       </c>
     </row>
     <row r="25">
@@ -2962,16 +2962,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.802275960170697</v>
+        <v>1.562291156702634</v>
       </c>
       <c r="C28" t="n">
-        <v>0.3423235436959162</v>
+        <v>2.411521838998778</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>0.2006829481523934</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.5630823226894625</v>
+        <v>7.678206006518048</v>
       </c>
     </row>
     <row r="29">
@@ -2981,16 +2981,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.2509369727554126</v>
+        <v>0.6920599324162882</v>
       </c>
       <c r="C29" t="n">
-        <v>0.9316770186335404</v>
+        <v>3.045241197469053</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>0.3379190118601669</v>
       </c>
       <c r="E29" t="n">
-        <v>0.2796642826598967</v>
+        <v>2.954740005904787</v>
       </c>
     </row>
     <row r="30">
@@ -3000,16 +3000,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.116327327238991</v>
+        <v>-1.634849746592639</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1804422908710093</v>
+        <v>0.1101246286731279</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0.5746237211426026</v>
       </c>
       <c r="E30" t="n">
-        <v>0.846919783422578</v>
+        <v>0.8075222579910346</v>
       </c>
     </row>
     <row r="31">
@@ -3019,16 +3019,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.2081315608795512</v>
+        <v>-1.625429956493171</v>
       </c>
       <c r="C31" t="n">
-        <v>0.105348160112252</v>
+        <v>-9.761830810105872</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>0.4221694011159169</v>
       </c>
       <c r="E31" t="n">
-        <v>0.8045796031751061</v>
+        <v>0.7129201767421751</v>
       </c>
     </row>
     <row r="33">
@@ -3067,16 +3067,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.28924040832123</v>
+        <v>0.2893266001796041</v>
       </c>
       <c r="C36" t="n">
         <v>0.424493821775237</v>
       </c>
       <c r="D36" t="n">
-        <v>0.3711621490252057</v>
+        <v>0.369594284303138</v>
       </c>
       <c r="E36" t="n">
-        <v>5.537502272379353</v>
+        <v>5.629004335106292</v>
       </c>
     </row>
     <row r="37">
@@ -3086,16 +3086,16 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.4465714491964846</v>
+        <v>0.4450949973902936</v>
       </c>
       <c r="C37" t="n">
         <v>0.3940320797542462</v>
       </c>
       <c r="D37" t="n">
-        <v>0.3551235110940761</v>
+        <v>0.3543542687321643</v>
       </c>
       <c r="E37" t="n">
-        <v>2.783482423886448</v>
+        <v>2.794720859404019</v>
       </c>
     </row>
     <row r="38">
@@ -3105,16 +3105,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4968017309259684</v>
+        <v>0.5003605303633228</v>
       </c>
       <c r="C38" t="n">
         <v>0.4165741188553942</v>
       </c>
       <c r="D38" t="n">
-        <v>0.4736382371392849</v>
+        <v>0.4730798942757271</v>
       </c>
       <c r="E38" t="n">
-        <v>0.8719091620666</v>
+        <v>0.8696770173651438</v>
       </c>
     </row>
     <row r="39">
@@ -3124,16 +3124,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7046820008927546</v>
+        <v>0.7019293361352302</v>
       </c>
       <c r="C39" t="n">
         <v>0.4805855207927329</v>
       </c>
       <c r="D39" t="n">
-        <v>0.5552345226750243</v>
+        <v>0.557099530957774</v>
       </c>
       <c r="E39" t="n">
-        <v>0.7147943042298349</v>
+        <v>0.7145237832584861</v>
       </c>
     </row>
   </sheetData>
@@ -3291,16 +3291,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8.629050845812984</v>
+        <v>8.590382031102974</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6933273381294964</v>
+        <v>0.9893599999170595</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>0.0653977881421632</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0311440905593387</v>
+        <v>0.04881948701955995</v>
       </c>
     </row>
     <row r="13">
@@ -3310,16 +3310,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-1.200968492146204</v>
+        <v>-0.9467471786367323</v>
       </c>
       <c r="C13" t="n">
-        <v>0.973929856115108</v>
+        <v>1.014177882436095</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>0.1576501876428697</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.02340377225684139</v>
+        <v>0.04615543838473526</v>
       </c>
     </row>
     <row r="14">
@@ -3329,16 +3329,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-2.635924524618226</v>
+        <v>-3.263582168010267</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.2442176258992806</v>
+        <v>-0.4419344125195142</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0.5194059593027166</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1898603455062634</v>
+        <v>0.1846279630766727</v>
       </c>
     </row>
     <row r="15">
@@ -3348,16 +3348,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-3.792157829048553</v>
+        <v>-3.380052684455976</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.4230395683453237</v>
+        <v>-0.56160346983364</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>0.2575460649122508</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8646875173099168</v>
+        <v>0.7203971115190322</v>
       </c>
     </row>
     <row r="17">
@@ -3399,10 +3399,10 @@
         <v>2.325373134328358</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2590437963725477</v>
+        <v>0.2660109893901302</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3320836105230778</v>
+        <v>0.3330691557316883</v>
       </c>
       <c r="E20" t="n">
         <v>0.02473569153936888</v>
@@ -3418,10 +3418,10 @@
         <v>0.04477611940298507</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4071310809324409</v>
+        <v>0.407183806181261</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2831466149704007</v>
+        <v>0.2836963541142133</v>
       </c>
       <c r="E21" t="n">
         <v>0.03619168535347992</v>
@@ -3437,10 +3437,10 @@
         <v>-1.194029850746269</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2131786128969048</v>
+        <v>0.2036321391905742</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1600574833106403</v>
+        <v>0.1607374245503783</v>
       </c>
       <c r="E22" t="n">
         <v>0.1961212157576122</v>
@@ -3456,10 +3456,10 @@
         <v>-0.1761194029850746</v>
       </c>
       <c r="C23" t="n">
-        <v>0.120646509798107</v>
+        <v>0.1231730652380346</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2247122911958814</v>
+        <v>0.2224970656037201</v>
       </c>
       <c r="E23" t="n">
         <v>0.7429514073495395</v>
@@ -3501,16 +3501,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>8.629050845812984</v>
+        <v>8.590382031102974</v>
       </c>
       <c r="C28" t="n">
-        <v>1.624126118104511</v>
+        <v>2.31758554394844</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>0.6804259620813287</v>
       </c>
       <c r="E28" t="n">
-        <v>-5.034217361704123</v>
+        <v>7.891317573556925</v>
       </c>
     </row>
     <row r="29">
@@ -3520,16 +3520,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.529018767649641</v>
+        <v>-1.205355689030585</v>
       </c>
       <c r="C29" t="n">
-        <v>0.973929856115108</v>
+        <v>1.014177882436095</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>0.3138473464407013</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.10619481866405</v>
+        <v>2.181567408623068</v>
       </c>
     </row>
     <row r="30">
@@ -3539,16 +3539,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-5.3895870573811</v>
+        <v>-6.672937729867451</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.375912717093803</v>
+        <v>-0.6802488771059401</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0.5194059593027166</v>
       </c>
       <c r="E30" t="n">
-        <v>0.8059707110784282</v>
+        <v>0.7837588743930665</v>
       </c>
     </row>
     <row r="31">
@@ -3558,16 +3558,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-17.97755583675392</v>
+        <v>-16.02388102111856</v>
       </c>
       <c r="C31" t="n">
-        <v>-1.387156316537657</v>
+        <v>-1.841510484743313</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>0.4848024379757294</v>
       </c>
       <c r="E31" t="n">
-        <v>0.8646875173099168</v>
+        <v>0.7203971115190322</v>
       </c>
     </row>
     <row r="33">
@@ -3609,10 +3609,10 @@
         <v>2.325373134328358</v>
       </c>
       <c r="C36" t="n">
-        <v>0.6068126443083096</v>
+        <v>0.6231333625714308</v>
       </c>
       <c r="D36" t="n">
-        <v>3.455136887663741</v>
+        <v>3.465390912544303</v>
       </c>
       <c r="E36" t="n">
         <v>3.998345932240082</v>
@@ -3628,10 +3628,10 @@
         <v>0.05700693012131973</v>
       </c>
       <c r="C37" t="n">
-        <v>0.4071310809324409</v>
+        <v>0.407183806181261</v>
       </c>
       <c r="D37" t="n">
-        <v>0.5636835267423573</v>
+        <v>0.5647779381991394</v>
       </c>
       <c r="E37" t="n">
         <v>1.71062401297449</v>
@@ -3647,10 +3647,10 @@
         <v>-2.441393055683503</v>
       </c>
       <c r="C38" t="n">
-        <v>0.3281358227330126</v>
+        <v>0.3134413842935394</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1600574833106403</v>
+        <v>0.1607374245503783</v>
       </c>
       <c r="E38" t="n">
         <v>0.8325485519382138</v>
@@ -3666,10 +3666,10 @@
         <v>-0.8349326541333164</v>
       </c>
       <c r="C39" t="n">
-        <v>0.3956026354443881</v>
+        <v>0.4038872678991881</v>
       </c>
       <c r="D39" t="n">
-        <v>0.4229964323158769</v>
+        <v>0.4188265112257917</v>
       </c>
       <c r="E39" t="n">
         <v>0.7429514073495395</v>
@@ -3830,16 +3830,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>0.5809260132648694</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>0.0178003365767932</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.003201876010140238</v>
+        <v>0.03223361383939326</v>
       </c>
     </row>
     <row r="13">
@@ -3849,16 +3849,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2852878026557504</v>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>0.1699941621355088</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.006569010136932875</v>
+        <v>0.03949891012805253</v>
       </c>
     </row>
     <row r="14">
@@ -3868,16 +3868,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.0583795717806389</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0.5073607964626807</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2065726458154992</v>
+        <v>0.2252386157157671</v>
       </c>
     </row>
     <row r="15">
@@ -3887,16 +3887,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>0.07540661229874139</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>0.3048447048250174</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8031982403315739</v>
+        <v>0.703028860316787</v>
       </c>
     </row>
     <row r="17">
@@ -4040,16 +4040,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>0.5809260132648694</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>0.3725810912366588</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.5787785823158498</v>
+        <v>5.826623286409981</v>
       </c>
     </row>
     <row r="29">
@@ -4059,16 +4059,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.3763055348751213</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>0.4343631016359732</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.3093625479489823</v>
+        <v>1.860171201399237</v>
       </c>
     </row>
     <row r="30">
@@ -4078,16 +4078,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>0.1276142556011354</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0.5073607964626807</v>
       </c>
       <c r="E30" t="n">
-        <v>0.6825697066939651</v>
+        <v>0.7442469222308359</v>
       </c>
     </row>
     <row r="31">
@@ -4097,16 +4097,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.336713480926883</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>0.5311067553414009</v>
       </c>
       <c r="E31" t="n">
-        <v>0.8031982403315739</v>
+        <v>0.703028860316787</v>
       </c>
     </row>
     <row r="33">
@@ -4369,16 +4369,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.053675568783354</v>
+        <v>0.920655664193457</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.6403654235730447</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3326791297984165</v>
+        <v>0.0320277331719265</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>0.03543592470164662</v>
       </c>
     </row>
     <row r="13">
@@ -4388,16 +4388,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2071884764658548</v>
+        <v>0.1309081598888129</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0.6923810950692836</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.2326525181291995</v>
+        <v>0.1498662681731651</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>0.04738663552127795</v>
       </c>
     </row>
     <row r="14">
@@ -4407,16 +4407,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.2235688143084041</v>
+        <v>0.06482950931969125</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>-0.2533313149477468</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8499101856163926</v>
+        <v>0.5189663447019479</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>0.2344850918342843</v>
       </c>
     </row>
     <row r="15">
@@ -4426,16 +4426,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.03729523094080511</v>
+        <v>-0.1163933334019613</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>-0.07941520369458149</v>
       </c>
       <c r="D15" t="n">
-        <v>0.05006320271439029</v>
+        <v>0.2991396539529605</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0.6826923479427908</v>
       </c>
     </row>
     <row r="17">
@@ -4579,16 +4579,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.053675568783354</v>
+        <v>0.920655664193457</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>1.516098466461647</v>
       </c>
       <c r="D28" t="n">
-        <v>7.952894899430387</v>
+        <v>0.765642244939358</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>6.254590385731068</v>
       </c>
     </row>
     <row r="29">
@@ -4598,16 +4598,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.2682390149722286</v>
+        <v>0.1694817996607508</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>0.6923810950692836</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.657277619908081</v>
+        <v>0.4233942741795807</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>2.689063764521352</v>
       </c>
     </row>
     <row r="30">
@@ -4617,16 +4617,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.501811563243353</v>
+        <v>0.1455131276544543</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>-0.4173405613850337</v>
       </c>
       <c r="D30" t="n">
-        <v>0.8499101856163926</v>
+        <v>0.5189663447019479</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>0.7373191103501078</v>
       </c>
     </row>
     <row r="31">
@@ -4636,16 +4636,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.168368945962442</v>
+        <v>-0.5254565360661705</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>-0.2430576398359067</v>
       </c>
       <c r="D31" t="n">
-        <v>0.08622814161335801</v>
+        <v>0.515233845313145</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0.6826923479427908</v>
       </c>
     </row>
     <row r="33">
@@ -4908,16 +4908,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>0.5780838751979742</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.1984544778273259</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>0.03084365761844996</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.5863309352517986</v>
+        <v>0.04316186339762544</v>
       </c>
     </row>
     <row r="13">
@@ -4927,16 +4927,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2067528312395392</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0.6328272039544555</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>0.1605265455588336</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.0539568345323741</v>
+        <v>0.05383388535083453</v>
       </c>
     </row>
     <row r="14">
@@ -4946,16 +4946,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.1577869741922953</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.1425842781126906</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0.5180024972935782</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3866906474820144</v>
+        <v>0.2144063415650408</v>
       </c>
     </row>
     <row r="15">
@@ -4965,16 +4965,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>0.05737631937019126</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>0.02613404010552803</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>0.2906272995291383</v>
       </c>
       <c r="E15" t="n">
-        <v>1.253597122302158</v>
+        <v>0.6885979096864995</v>
       </c>
     </row>
     <row r="17">
@@ -5118,16 +5118,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>0.5780838751979742</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.4677471622602228</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>0.7342316856924276</v>
       </c>
       <c r="E28" t="n">
-        <v>-142.7881568914357</v>
+        <v>10.51113381882225</v>
       </c>
     </row>
     <row r="29">
@@ -5137,16 +5137,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.2706349150916895</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>0.6328272039544555</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>0.430610872790878</v>
       </c>
       <c r="E29" t="n">
-        <v>-3.576005333917253</v>
+        <v>3.567856840166708</v>
       </c>
     </row>
     <row r="30">
@@ -5156,16 +5156,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>0.3449719804919912</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.2271896442290487</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0.5180024972935782</v>
       </c>
       <c r="E30" t="n">
-        <v>1.374893086868186</v>
+        <v>0.7623297814881457</v>
       </c>
     </row>
     <row r="31">
@@ -5175,16 +5175,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.2633670428057657</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.0804767183606937</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>0.5098394605414608</v>
       </c>
       <c r="E31" t="n">
-        <v>1.253597122302158</v>
+        <v>0.6885979096864995</v>
       </c>
     </row>
     <row r="33">
@@ -5447,16 +5447,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>3.887903816191382</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.1932207904148097</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2392149160665114</v>
+        <v>10.26142664796405</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.01980037182102047</v>
+        <v>0.04287159771199094</v>
       </c>
     </row>
     <row r="13">
@@ -5466,16 +5466,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>-0.93453078261097</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0.8278004540111114</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.02597364440957172</v>
+        <v>-35.39131071683878</v>
       </c>
       <c r="E13" t="n">
-        <v>0.02346443333393499</v>
+        <v>0.05620077233177746</v>
       </c>
     </row>
     <row r="14">
@@ -5485,16 +5485,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>-2.162549300882138</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.1014811939152407</v>
       </c>
       <c r="D14" t="n">
-        <v>1.085839442535339</v>
+        <v>18.70027257776597</v>
       </c>
       <c r="E14" t="n">
-        <v>0.06001480064256449</v>
+        <v>0.2057901547255912</v>
       </c>
     </row>
     <row r="15">
@@ -5504,16 +5504,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>0.2091762673017261</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>-0.1225024383411619</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1793491179407438</v>
+        <v>7.429611491108764</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9363211378445211</v>
+        <v>0.6951374752306406</v>
       </c>
     </row>
     <row r="17">
@@ -5552,16 +5552,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.3622396486587982</v>
+        <v>0.3678232588756127</v>
       </c>
       <c r="C20" t="n">
         <v>0.2002459331309915</v>
       </c>
       <c r="D20" t="n">
-        <v>0.03762260747365872</v>
+        <v>0.03895204635859873</v>
       </c>
       <c r="E20" t="n">
-        <v>0.04775310112685979</v>
+        <v>0.04907675747505563</v>
       </c>
     </row>
     <row r="21">
@@ -5571,16 +5571,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2730139976952095</v>
+        <v>0.2741732233818329</v>
       </c>
       <c r="C21" t="n">
         <v>0.3895175249038547</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1634563217148957</v>
+        <v>0.1636278195888542</v>
       </c>
       <c r="E21" t="n">
-        <v>0.07620449919953715</v>
+        <v>0.07696670582495088</v>
       </c>
     </row>
     <row r="22">
@@ -5590,16 +5590,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2248269097184258</v>
+        <v>0.2239239368589873</v>
       </c>
       <c r="C22" t="n">
         <v>0.2591014152472906</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5127051109133579</v>
+        <v>0.511827537581339</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2216309759575338</v>
+        <v>0.2214460201483668</v>
       </c>
     </row>
     <row r="23">
@@ -5609,16 +5609,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1399194439275664</v>
+        <v>0.1340795808835669</v>
       </c>
       <c r="C23" t="n">
         <v>0.1511351267178632</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2862159598980878</v>
+        <v>0.2855925964712082</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6544114237160695</v>
+        <v>0.652510516551627</v>
       </c>
     </row>
     <row r="25">
@@ -5657,16 +5657,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>3.887903816191382</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.4342875912911963</v>
       </c>
       <c r="D28" t="n">
-        <v>-5.849223055966131</v>
+        <v>250.9098275447349</v>
       </c>
       <c r="E28" t="n">
-        <v>-5.169808851545928</v>
+        <v>11.1936264295841</v>
       </c>
     </row>
     <row r="29">
@@ -5676,16 +5676,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>-1.24090127198062</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>0.8278004540111114</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.06570230943787612</v>
+        <v>-89.52501279615788</v>
       </c>
       <c r="E29" t="n">
-        <v>1.289557545823688</v>
+        <v>3.088680174379</v>
       </c>
     </row>
     <row r="30">
@@ -5695,16 +5695,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>-4.616122136682833</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.1591745961019511</v>
       </c>
       <c r="D30" t="n">
-        <v>1.085839442535339</v>
+        <v>18.70027257776597</v>
       </c>
       <c r="E30" t="n">
-        <v>0.2322739110478053</v>
+        <v>0.79646493167462</v>
       </c>
     </row>
     <row r="31">
@@ -5714,16 +5714,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.9092517715573308</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>-0.3596052746501501</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3012806661965362</v>
+        <v>12.4806763775791</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9363211378445211</v>
+        <v>0.6951374752306406</v>
       </c>
     </row>
     <row r="33">
@@ -5762,16 +5762,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.3622396486587982</v>
+        <v>0.3678232588756127</v>
       </c>
       <c r="C36" t="n">
         <v>0.4500774672260669</v>
       </c>
       <c r="D36" t="n">
-        <v>0.9199385501500329</v>
+        <v>0.9524456559156571</v>
       </c>
       <c r="E36" t="n">
-        <v>12.46817014983126</v>
+        <v>12.81377226110289</v>
       </c>
     </row>
     <row r="37">
@@ -5781,16 +5781,16 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.3625171297856856</v>
+        <v>0.3640563884765814</v>
       </c>
       <c r="C37" t="n">
         <v>0.3895175249038547</v>
       </c>
       <c r="D37" t="n">
-        <v>0.4134752004586403</v>
+        <v>0.4139090173772473</v>
       </c>
       <c r="E37" t="n">
-        <v>4.18804432947277</v>
+        <v>4.229933655811522</v>
       </c>
     </row>
     <row r="38">
@@ -5800,16 +5800,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4799097409940533</v>
+        <v>0.4779822783444955</v>
       </c>
       <c r="C38" t="n">
         <v>0.4064039998965515</v>
       </c>
       <c r="D38" t="n">
-        <v>0.5127051109133579</v>
+        <v>0.511827537581339</v>
       </c>
       <c r="E38" t="n">
-        <v>0.8577732999830678</v>
+        <v>0.8570574697427563</v>
       </c>
     </row>
     <row r="39">
@@ -5819,16 +5819,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.608204763893913</v>
+        <v>0.5828199251313517</v>
       </c>
       <c r="C39" t="n">
         <v>0.4436563834044168</v>
       </c>
       <c r="D39" t="n">
-        <v>0.4808015565633695</v>
+        <v>0.4797543958597695</v>
       </c>
       <c r="E39" t="n">
-        <v>0.6544114237160695</v>
+        <v>0.652510516551627</v>
       </c>
     </row>
   </sheetData>
@@ -5986,16 +5986,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>0.7236607005080751</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.1483072600023072</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>0.05081863225063247</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>0.05813699490977348</v>
       </c>
     </row>
     <row r="13">
@@ -6005,16 +6005,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.04139114612281663</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0.6106418020591043</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>0.2087965185425484</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>0.07019064569204767</v>
       </c>
     </row>
     <row r="14">
@@ -6024,16 +6024,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.1770441663112987</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.003034862840886947</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0.5450672565646337</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>0.2164955579789818</v>
       </c>
     </row>
     <row r="15">
@@ -6043,16 +6043,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>0.05790398705780958</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>0.2380160750977016</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>0.1953175926421855</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0.6551768014191971</v>
       </c>
     </row>
     <row r="17">
@@ -6196,16 +6196,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>0.7236607005080751</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.3547611470185599</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>1.338216039445777</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>9.94524548951471</v>
       </c>
     </row>
     <row r="29">
@@ -6215,16 +6215,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.0507743244572824</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>0.6106418020591043</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>0.5280824779267561</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>4.153013162125351</v>
       </c>
     </row>
     <row r="30">
@@ -6234,16 +6234,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>0.3516082240495172</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.004764672166742445</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0.5450672565646337</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>0.7574422497622745</v>
       </c>
     </row>
     <row r="31">
@@ -6253,16 +6253,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.2418511045463422</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.7189345993432338</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>0.3489229850279395</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0.6551768014191971</v>
       </c>
     </row>
     <row r="33">
@@ -6525,16 +6525,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>5.022338350055741</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>2.927580275229358</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>-0.01084181226386791</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>0.05339397227856402</v>
       </c>
     </row>
     <row r="13">
@@ -6544,16 +6544,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>-3.488888888888889</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>5.663016055045872</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>0.09972912946999439</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>0.05087483626917208</v>
       </c>
     </row>
     <row r="14">
@@ -6563,16 +6563,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>-2.054643564969652</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>-1.69420871559633</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0.659351314878405</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>0.2379418822561189</v>
       </c>
     </row>
     <row r="15">
@@ -6582,16 +6582,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>1.521194103802799</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>-5.896387614678899</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>0.2517613679154686</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0.6577893091961454</v>
       </c>
     </row>
     <row r="17">
@@ -6630,13 +6630,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.3758036332888496</v>
+        <v>0.423046085661676</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1895881977793653</v>
+        <v>0.1917367518923852</v>
       </c>
       <c r="D20" t="n">
-        <v>0.03534533847942064</v>
+        <v>0.05375360636593947</v>
       </c>
       <c r="E20" t="n">
         <v>0.05386733904200881</v>
@@ -6649,13 +6649,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.273358674805004</v>
+        <v>0.2467841806322503</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3730106337549876</v>
+        <v>0.3721897615755299</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1552153292447963</v>
+        <v>0.1614329310325581</v>
       </c>
       <c r="E21" t="n">
         <v>0.07404269782141433</v>
@@ -6668,13 +6668,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1982598938414692</v>
+        <v>0.1837812911815412</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2698577050447119</v>
+        <v>0.2690394460098595</v>
       </c>
       <c r="D22" t="n">
-        <v>0.526036309849386</v>
+        <v>0.4913759463513084</v>
       </c>
       <c r="E22" t="n">
         <v>0.2568693884356802</v>
@@ -6687,13 +6687,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1525777980646774</v>
+        <v>0.1463884425245323</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1675434634209352</v>
+        <v>0.1670340405222254</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2834030224263968</v>
+        <v>0.2934375162501939</v>
       </c>
       <c r="E23" t="n">
         <v>0.6152205747008969</v>
@@ -6735,16 +6735,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>5.022338350055741</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>6.710220496732627</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>-0.2105009685152512</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>7.471075499555828</v>
       </c>
     </row>
     <row r="29">
@@ -6754,16 +6754,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>-4.67382003683467</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>5.663016055045872</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>0.260798904201007</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>2.367111766909624</v>
       </c>
     </row>
     <row r="30">
@@ -6773,16 +6773,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>-4.499759112985111</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>-2.680411827060347</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0.659351314878405</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>0.8045185933584075</v>
       </c>
     </row>
     <row r="31">
@@ -6792,16 +6792,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>6.895874917383334</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>-17.7055653717141</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>0.4498235521364144</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0.6577893091961454</v>
       </c>
     </row>
     <row r="33">
@@ -6840,13 +6840,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.3758036332888496</v>
+        <v>0.423046085661676</v>
       </c>
       <c r="C36" t="n">
-        <v>0.4345495224987567</v>
+        <v>0.4394741600806914</v>
       </c>
       <c r="D36" t="n">
-        <v>0.686253165184679</v>
+        <v>1.043661882887192</v>
       </c>
       <c r="E36" t="n">
         <v>7.537310669515194</v>
@@ -6859,13 +6859,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.366199467003688</v>
+        <v>0.3305994787871191</v>
       </c>
       <c r="C37" t="n">
-        <v>0.3730106337549876</v>
+        <v>0.3721897615755299</v>
       </c>
       <c r="D37" t="n">
-        <v>0.4058993395146465</v>
+        <v>0.4221588189829235</v>
       </c>
       <c r="E37" t="n">
         <v>3.445069392252919</v>
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4341978235362632</v>
+        <v>0.4024890515754859</v>
       </c>
       <c r="C38" t="n">
-        <v>0.426942547022968</v>
+        <v>0.4256479773666873</v>
       </c>
       <c r="D38" t="n">
-        <v>0.526036309849386</v>
+        <v>0.4913759463513084</v>
       </c>
       <c r="E38" t="n">
         <v>0.8685154420971781</v>
@@ -6897,13 +6897,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6916654541281244</v>
+        <v>0.663607876520272</v>
       </c>
       <c r="C39" t="n">
-        <v>0.5030964614364662</v>
+        <v>0.5015667756314657</v>
       </c>
       <c r="D39" t="n">
-        <v>0.5063578867939773</v>
+        <v>0.5242865773356764</v>
       </c>
       <c r="E39" t="n">
         <v>0.6152205747008969</v>
@@ -7064,16 +7064,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8184818481848185</v>
+        <v>0.7198030756258442</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.2279642900748474</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>0.05009391310939093</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>0.05465716931277688</v>
       </c>
     </row>
     <row r="13">
@@ -7083,16 +7083,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1600660066006601</v>
+        <v>-0.03302903782557147</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0.5659001916803822</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>0.1618211050738123</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>0.06862368667895005</v>
       </c>
     </row>
     <row r="14">
@@ -7102,16 +7102,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.103960396039604</v>
+        <v>0.2616404775432424</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>-0.06922070506929222</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0.5252319658828517</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>0.2403121991920511</v>
       </c>
     </row>
     <row r="15">
@@ -7121,16 +7121,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.08250825082508251</v>
+        <v>0.05158548465648492</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>0.2753562233140626</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>0.2628530159339452</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0.6364069448162221</v>
       </c>
     </row>
     <row r="17">
@@ -7274,16 +7274,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8184818481848185</v>
+        <v>0.7198030756258442</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.4884876365891254</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>1.444469326104682</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>9.445754091469512</v>
       </c>
     </row>
     <row r="29">
@@ -7293,16 +7293,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.2116406585468454</v>
+        <v>-0.04367127952415467</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>0.5659001916803822</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>0.5125751581923145</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>4.091415277530488</v>
       </c>
     </row>
     <row r="30">
@@ -7312,16 +7312,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.2227273147263882</v>
+        <v>0.5605450075886249</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>-0.1093180945907199</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0.5252319658828517</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>0.7672518641041808</v>
       </c>
     </row>
     <row r="31">
@@ -7331,16 +7331,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.3572507892113879</v>
+        <v>0.2233589358772199</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.8056824108929261</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>0.4535327297163543</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0.6364069448162221</v>
       </c>
     </row>
     <row r="33">
@@ -7603,16 +7603,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>0.5761538825469562</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.3021160183736051</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>0.02787772879039941</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>0.03707120374162635</v>
       </c>
     </row>
     <row r="13">
@@ -7622,16 +7622,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.1522030049271072</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>2.225354779809393</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>0.05292621562925644</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>0.001795501040148601</v>
       </c>
     </row>
     <row r="14">
@@ -7641,16 +7641,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.1316024250288935</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>-0.8857012995550805</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0.6461278984837076</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>0.2421869143485389</v>
       </c>
     </row>
     <row r="15">
@@ -7660,16 +7660,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>0.140040687497043</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>-0.6417694986279175</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>0.2730681570966367</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0.7189463808696864</v>
       </c>
     </row>
     <row r="17">
@@ -7813,16 +7813,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>0.5761538825469562</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.6279895522251848</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>0.7000479840819424</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>5.936370529969014</v>
       </c>
     </row>
     <row r="29">
@@ -7832,16 +7832,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.2030921093422273</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>2.225354779809393</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>0.1643893293413707</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>0.1014641006053231</v>
       </c>
     </row>
     <row r="30">
@@ -7851,16 +7851,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>0.2867057365673121</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>-1.406655895973997</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0.6461278984837076</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>0.7655527583872828</v>
       </c>
     </row>
     <row r="31">
@@ -7870,16 +7870,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.6249995562014544</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>-1.897676043893093</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>0.4758275141966692</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0.7189463808696864</v>
       </c>
     </row>
     <row r="33">
@@ -8142,16 +8142,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>0.8809523809523809</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.6421397204917538</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1488294314381271</v>
+        <v>0.07084519369096617</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>0.05077008299717659</v>
       </c>
     </row>
     <row r="13">
@@ -8161,16 +8161,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.163265306122449</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0.9237714797665709</v>
       </c>
       <c r="D13" t="n">
-        <v>0.04013377926421405</v>
+        <v>0.122268410191593</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>0.05087976969470961</v>
       </c>
     </row>
     <row r="14">
@@ -8183,13 +8183,13 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>-0.8708723950767744</v>
       </c>
       <c r="D14" t="n">
-        <v>0.81438127090301</v>
+        <v>0.5667242591066823</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>0.2384819208818426</v>
       </c>
     </row>
     <row r="15">
@@ -8199,16 +8199,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>-0.04421768707482993</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>0.3049611948184494</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.003344481605351171</v>
+        <v>0.2401621370107584</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0.6598682264262714</v>
       </c>
     </row>
     <row r="17">
@@ -8253,7 +8253,7 @@
         <v>0.2136945791128043</v>
       </c>
       <c r="D20" t="n">
-        <v>0.06943284948916037</v>
+        <v>0.07258188851035689</v>
       </c>
       <c r="E20" t="n">
         <v>0.04765806798079559</v>
@@ -8272,7 +8272,7 @@
         <v>0.3887550273403349</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1719062088360158</v>
+        <v>0.1737237490545728</v>
       </c>
       <c r="E21" t="n">
         <v>0.06890629532798917</v>
@@ -8291,7 +8291,7 @@
         <v>0.2442276304507072</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4776055145505075</v>
+        <v>0.4730494655484386</v>
       </c>
       <c r="E22" t="n">
         <v>0.2445736677061377</v>
@@ -8310,7 +8310,7 @@
         <v>0.1533227630961536</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2810554271243167</v>
+        <v>0.280644896886632</v>
       </c>
       <c r="E23" t="n">
         <v>0.6388619689850777</v>
@@ -8352,16 +8352,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>0.8809523809523809</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>1.286539310169832</v>
       </c>
       <c r="D28" t="n">
-        <v>3.380128107512231</v>
+        <v>1.608995130620627</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>9.18343862052232</v>
       </c>
     </row>
     <row r="29">
@@ -8371,16 +8371,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.2070326897317122</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>0.9237714797665709</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1215149996989868</v>
+        <v>0.3701980252050399</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>2.89990762400904</v>
       </c>
     </row>
     <row r="30">
@@ -8393,13 +8393,13 @@
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>-1.48898455187073</v>
       </c>
       <c r="D30" t="n">
-        <v>0.81438127090301</v>
+        <v>0.5667242591066823</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>0.746443803928756</v>
       </c>
     </row>
     <row r="31">
@@ -8409,16 +8409,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>-0.1946460409578971</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.9301183803256443</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.005646433115671978</v>
+        <v>0.405461773620881</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0.6598682264262714</v>
       </c>
     </row>
     <row r="33">
@@ -8463,7 +8463,7 @@
         <v>0.4281412091877446</v>
       </c>
       <c r="D36" t="n">
-        <v>1.576918784646071</v>
+        <v>1.648437940530398</v>
       </c>
       <c r="E36" t="n">
         <v>8.620528394618848</v>
@@ -8482,7 +8482,7 @@
         <v>0.3887550273403349</v>
       </c>
       <c r="D37" t="n">
-        <v>0.5204888076311469</v>
+        <v>0.5259918627423257</v>
       </c>
       <c r="E37" t="n">
         <v>3.927334820161959</v>
@@ -8501,7 +8501,7 @@
         <v>0.4175711286026441</v>
       </c>
       <c r="D38" t="n">
-        <v>0.4776055145505075</v>
+        <v>0.4730494655484386</v>
       </c>
       <c r="E38" t="n">
         <v>0.7655108537717109</v>
@@ -8520,7 +8520,7 @@
         <v>0.4676277588791092</v>
       </c>
       <c r="D39" t="n">
-        <v>0.4745012406451682</v>
+        <v>0.473808149217983</v>
       </c>
       <c r="E39" t="n">
         <v>0.6388619689850777</v>
@@ -8681,16 +8681,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>1.363671723396743</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.05111266044140673</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1033210332103321</v>
+        <v>0.009252962637120308</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>0.02148318506397265</v>
       </c>
     </row>
     <row r="13">
@@ -8700,16 +8700,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.0797187197867483</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0.6731424228223972</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2047970479704797</v>
+        <v>-0.07828533981396477</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>-0.003637562529530231</v>
       </c>
     </row>
     <row r="14">
@@ -8719,16 +8719,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>-0.08532108314748207</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.1609671630873327</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8247232472324724</v>
+        <v>0.6680765144036457</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>0.2944055946276086</v>
       </c>
     </row>
     <row r="15">
@@ -8738,16 +8738,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>-0.3580693600360093</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>0.1147777536488633</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1328413284132841</v>
+        <v>0.4009558627731987</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0.6877487828379492</v>
       </c>
     </row>
     <row r="17">
@@ -8891,16 +8891,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>1.363671723396743</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.1102342338962726</v>
       </c>
       <c r="D28" t="n">
-        <v>2.832606041253225</v>
+        <v>0.253675336482953</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>3.723624866086029</v>
       </c>
     </row>
     <row r="29">
@@ -8910,16 +8910,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.107760816612085</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>0.6731424228223972</v>
       </c>
       <c r="D29" t="n">
-        <v>0.6190374997906648</v>
+        <v>-0.2366321268248202</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>-0.2044943392301727</v>
       </c>
     </row>
     <row r="30">
@@ -8929,16 +8929,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>-0.1926995420038712</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.2623964256490979</v>
       </c>
       <c r="D30" t="n">
-        <v>0.8247232472324724</v>
+        <v>0.6680765144036457</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>0.9060162707197016</v>
       </c>
     </row>
     <row r="31">
@@ -8948,16 +8948,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>-1.69083536055343</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.3533700729158318</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.2344011459414365</v>
+        <v>0.7074945337310906</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0.6877487828379492</v>
       </c>
     </row>
     <row r="33">
@@ -9220,16 +9220,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>1.320754716981132</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>-0.3878145295866815</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1857142857142857</v>
+        <v>0.01164386608755844</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>0.04506723558667119</v>
       </c>
     </row>
     <row r="13">
@@ -9239,16 +9239,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>-0.0646900269541779</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>1.765769345516181</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.3809523809523809</v>
+        <v>0.1723848911049477</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>0.06453725592623512</v>
       </c>
     </row>
     <row r="14">
@@ -9258,16 +9258,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>-0.3234501347708895</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>-4.786587065067997e-05</v>
       </c>
       <c r="D14" t="n">
-        <v>2.70952380952381</v>
+        <v>0.5599817251553062</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>0.2335679143995406</v>
       </c>
     </row>
     <row r="15">
@@ -9277,16 +9277,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>0.0673854447439353</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>-0.3779069500588488</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.142857142857143</v>
+        <v>0.255989517652188</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0.6568275940875528</v>
       </c>
     </row>
     <row r="17">
@@ -9430,16 +9430,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>1.320754716981132</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>-0.9076509426642444</v>
       </c>
       <c r="D28" t="n">
-        <v>-5.507124075078201</v>
+        <v>0.3452842360034292</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>7.693225319149398</v>
       </c>
     </row>
     <row r="29">
@@ -9449,16 +9449,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>-0.08356402723342005</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>1.765769345516181</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.183426632699226</v>
+        <v>0.5355127869224463</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>3.559088912273366</v>
       </c>
     </row>
     <row r="30">
@@ -9468,16 +9468,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>-0.7197010127140571</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>-7.974700919285953e-05</v>
       </c>
       <c r="D30" t="n">
-        <v>2.70952380952381</v>
+        <v>0.5599817251553062</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>0.6920174419022569</v>
       </c>
     </row>
     <row r="31">
@@ -9487,16 +9487,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.3118629748767691</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>-1.201059912475132</v>
       </c>
       <c r="D31" t="n">
-        <v>-2.049837115218542</v>
+        <v>0.4591447125915536</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0.6568275940875528</v>
       </c>
     </row>
     <row r="33">
@@ -9759,16 +9759,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>7.37926657565954</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.1410220857511585</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.05288461538461538</v>
+        <v>0.0658979864017228</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.2425951341235184</v>
+        <v>0.03617130327268817</v>
       </c>
     </row>
     <row r="13">
@@ -9778,16 +9778,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.1585608203219654</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>1.510917731132186</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4487179487179487</v>
+        <v>0.1343881893314092</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2437242669993762</v>
+        <v>0.05833491510599537</v>
       </c>
     </row>
     <row r="14">
@@ -9797,16 +9797,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>-4.014565024777245</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>-0.6978558089037113</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9375</v>
+        <v>0.5653361592511801</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.6436930754834684</v>
+        <v>0.225157289980035</v>
       </c>
     </row>
     <row r="15">
@@ -9816,16 +9816,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>-2.52326237120426</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>0.04591599202036693</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.3333333333333333</v>
+        <v>0.2343776650156879</v>
       </c>
       <c r="E15" t="n">
-        <v>1.642563942607611</v>
+        <v>0.680336491641282</v>
       </c>
     </row>
     <row r="17">
@@ -9969,16 +9969,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>7.37926657565954</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.293636767527728</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.274919808101917</v>
+        <v>1.588640620085285</v>
       </c>
       <c r="E28" t="n">
-        <v>-40.91347571292606</v>
+        <v>6.100261422384984</v>
       </c>
     </row>
     <row r="29">
@@ -9988,16 +9988,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.2053029703058621</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>1.510917731132186</v>
       </c>
       <c r="D29" t="n">
-        <v>1.354122500633007</v>
+        <v>0.4055511296415201</v>
       </c>
       <c r="E29" t="n">
-        <v>14.4190535062222</v>
+        <v>3.451171574131476</v>
       </c>
     </row>
     <row r="30">
@@ -10007,16 +10007,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>-9.299800594307261</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>-1.199071068437366</v>
       </c>
       <c r="D30" t="n">
-        <v>0.9375</v>
+        <v>0.5653361592511801</v>
       </c>
       <c r="E30" t="n">
-        <v>-2.041504430667783</v>
+        <v>0.7140974830996101</v>
       </c>
     </row>
     <row r="31">
@@ -10026,16 +10026,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>-11.41414664272734</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.1416294961353208</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5595889893970308</v>
+        <v>0.3934654821100939</v>
       </c>
       <c r="E31" t="n">
-        <v>1.642563942607611</v>
+        <v>0.680336491641282</v>
       </c>
     </row>
     <row r="33">
@@ -10298,16 +10298,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>0.7017152248164962</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.290167865707434</v>
+        <v>0.1345316436916705</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>0.009615933016728664</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1301989150090416</v>
+        <v>0.04801279838576853</v>
       </c>
     </row>
     <row r="13">
@@ -10317,16 +10317,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.1888169648903098</v>
       </c>
       <c r="C13" t="n">
-        <v>1.07673860911271</v>
+        <v>0.922802263500236</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>0.06752362605971234</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1301989150090416</v>
+        <v>0.06322971260309264</v>
       </c>
     </row>
     <row r="14">
@@ -10336,16 +10336,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>-0.1559610258774148</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.001182928497898778</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0.5660926299072954</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.1880650994575045</v>
+        <v>0.2401793984417688</v>
       </c>
     </row>
     <row r="15">
@@ -10355,16 +10355,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>0.2654288361706089</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2134292565947242</v>
+        <v>-0.05851683568980515</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>0.3567678110162637</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9276672694394213</v>
+        <v>0.6485780905693694</v>
       </c>
     </row>
     <row r="17">
@@ -10508,16 +10508,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>0.7017152248164962</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.6680510097398581</v>
+        <v>0.3097310592648466</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>0.2791227449067086</v>
       </c>
       <c r="E28" t="n">
-        <v>23.84032246924131</v>
+        <v>8.791475690007871</v>
       </c>
     </row>
     <row r="29">
@@ -10527,16 +10527,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.2461781966897396</v>
       </c>
       <c r="C29" t="n">
-        <v>1.07673860911271</v>
+        <v>0.922802263500236</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>0.2085584179221052</v>
       </c>
       <c r="E29" t="n">
-        <v>8.278516523491934</v>
+        <v>4.020373138470455</v>
       </c>
     </row>
     <row r="30">
@@ -10546,16 +10546,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>-0.3510522737906348</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.001992959047621582</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0.5660926299072954</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.5799512442457959</v>
+        <v>0.7406602361114073</v>
       </c>
     </row>
     <row r="31">
@@ -10565,16 +10565,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>1.199301078817985</v>
       </c>
       <c r="C31" t="n">
-        <v>0.6543163907723609</v>
+        <v>-0.1793967956355569</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>0.6179563820412086</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9276672694394213</v>
+        <v>0.6485780905693694</v>
       </c>
     </row>
     <row r="33">
@@ -10837,16 +10837,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>0.8240079028568351</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1017811704834606</v>
+        <v>0.01428656698445375</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1820396858177173</v>
+        <v>0.06712906564885153</v>
       </c>
     </row>
     <row r="13">
@@ -10856,16 +10856,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>-0.1173465868670587</v>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>0.05551431634651325</v>
       </c>
       <c r="E13" t="n">
-        <v>0.07322127082082378</v>
+        <v>0.06248292872237819</v>
       </c>
     </row>
     <row r="14">
@@ -10875,16 +10875,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.4222819872322227</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1.424936386768448</v>
+        <v>0.6741708360677561</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.1061527942161582</v>
+        <v>0.1975825961964013</v>
       </c>
     </row>
     <row r="15">
@@ -10894,16 +10894,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>-0.1289433032219992</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.3231552162849873</v>
+        <v>0.2560282806012769</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8508918375776171</v>
+        <v>0.6728054094323687</v>
       </c>
     </row>
     <row r="17">
@@ -10942,13 +10942,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.3524356944349782</v>
+        <v>0.3550424025006611</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2020609170147603</v>
+        <v>0.2027695747123955</v>
       </c>
       <c r="D20" t="n">
-        <v>0.05055751185561443</v>
+        <v>0.05279346377241942</v>
       </c>
       <c r="E20" t="n">
         <v>0.04853604199633629</v>
@@ -10961,13 +10961,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2884953710580245</v>
+        <v>0.2892775930485416</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3828764912286508</v>
+        <v>0.3830611386426441</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1632805410972903</v>
+        <v>0.1603254941536467</v>
       </c>
       <c r="E21" t="n">
         <v>0.0603243638391109</v>
@@ -10980,13 +10980,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2159761167320161</v>
+        <v>0.2137352830609821</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2575109407390364</v>
+        <v>0.2563208203952366</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4950142898334066</v>
+        <v>0.4999295118704465</v>
       </c>
       <c r="E22" t="n">
         <v>0.2315655523212633</v>
@@ -10999,13 +10999,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1430928177749812</v>
+        <v>0.1419447213898152</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1575516510175526</v>
+        <v>0.157848466249724</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2911476572136888</v>
+        <v>0.2869515302034875</v>
       </c>
       <c r="E23" t="n">
         <v>0.6595740418432889</v>
@@ -11047,16 +11047,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>0.8240079028568351</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>-2.52996977658009</v>
+        <v>0.3551205248482423</v>
       </c>
       <c r="E28" t="n">
-        <v>37.49302136345253</v>
+        <v>13.82594944160269</v>
       </c>
     </row>
     <row r="29">
@@ -11066,16 +11066,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>-0.1493498761414913</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>0.1721981118425409</v>
       </c>
       <c r="E29" t="n">
-        <v>5.254335714185897</v>
+        <v>4.483755611348319</v>
       </c>
     </row>
     <row r="30">
@@ -11085,16 +11085,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>0.9049722088573366</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>1.424936386768448</v>
+        <v>0.6741708360677561</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.3514017870252103</v>
+        <v>0.6540654713913069</v>
       </c>
     </row>
     <row r="31">
@@ -11104,16 +11104,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>-0.5451446858165685</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5432585549177438</v>
+        <v>0.4304109812507642</v>
       </c>
       <c r="E31" t="n">
-        <v>0.8508918375776171</v>
+        <v>0.6728054094323687</v>
       </c>
     </row>
     <row r="33">
@@ -11152,13 +11152,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.3524356944349782</v>
+        <v>0.3550424025006611</v>
       </c>
       <c r="C36" t="n">
-        <v>0.4019691453017205</v>
+        <v>0.4033789108973555</v>
       </c>
       <c r="D36" t="n">
-        <v>1.256705698767527</v>
+        <v>1.312284650596561</v>
       </c>
       <c r="E36" t="n">
         <v>9.996517250025676</v>
@@ -11171,13 +11171,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.3671751269913138</v>
+        <v>0.3681706800833797</v>
       </c>
       <c r="C37" t="n">
-        <v>0.3828764912286508</v>
+        <v>0.3830611386426441</v>
       </c>
       <c r="D37" t="n">
-        <v>0.506474774940604</v>
+        <v>0.4973086077680621</v>
       </c>
       <c r="E37" t="n">
         <v>4.328857663929558</v>
@@ -11190,13 +11190,13 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4628480241377636</v>
+        <v>0.4580458013144579</v>
       </c>
       <c r="C38" t="n">
-        <v>0.4200550985498577</v>
+        <v>0.4181137592154344</v>
       </c>
       <c r="D38" t="n">
-        <v>0.4950142898334066</v>
+        <v>0.4999295118704465</v>
       </c>
       <c r="E38" t="n">
         <v>0.7665605931528601</v>
@@ -11209,13 +11209,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6049658046548387</v>
+        <v>0.6001118988874263</v>
       </c>
       <c r="C39" t="n">
-        <v>0.4609454491531693</v>
+        <v>0.4618138350420199</v>
       </c>
       <c r="D39" t="n">
-        <v>0.4894504174925898</v>
+        <v>0.4823962782401913</v>
       </c>
       <c r="E39" t="n">
         <v>0.6595740418432889</v>
@@ -11376,16 +11376,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.914801350418154</v>
+        <v>1.295603947136522</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.2403181978421771</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.662034140719134</v>
+        <v>-0.3684083462121287</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.7896822977010793</v>
+        <v>0.0540453738724737</v>
       </c>
     </row>
     <row r="13">
@@ -11395,16 +11395,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-2.428234510070238</v>
+        <v>-0.3492914132989381</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0.574303516795716</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.7387772956660889</v>
+        <v>-0.0263641466924699</v>
       </c>
       <c r="E13" t="n">
-        <v>0.02439173120312214</v>
+        <v>0.100744063382535</v>
       </c>
     </row>
     <row r="14">
@@ -11414,16 +11414,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.898587694372843</v>
+        <v>0.2251708924389059</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.1204297636478841</v>
       </c>
       <c r="D14" t="n">
-        <v>3.47156130253205</v>
+        <v>1.177616160407668</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.3170925056405878</v>
+        <v>-0.1381847792734827</v>
       </c>
     </row>
     <row r="15">
@@ -11433,16 +11433,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-1.385154534720759</v>
+        <v>-0.1714834262764895</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>0.06494852171422273</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.07074986614682718</v>
+        <v>0.2171563324969314</v>
       </c>
       <c r="E15" t="n">
-        <v>2.082383072138545</v>
+        <v>0.9833953420184738</v>
       </c>
     </row>
     <row r="17">
@@ -11586,16 +11586,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3.914801350418154</v>
+        <v>1.295603947136522</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.4979507732816535</v>
       </c>
       <c r="D28" t="n">
-        <v>-45.26640866506721</v>
+        <v>-10.03380276415028</v>
       </c>
       <c r="E28" t="n">
-        <v>-138.0435284038113</v>
+        <v>9.447614724274233</v>
       </c>
     </row>
     <row r="29">
@@ -11605,16 +11605,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-2.993169242914309</v>
+        <v>-0.4305549199489017</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>0.574303516795716</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.949134050493582</v>
+        <v>-0.06955716740613906</v>
       </c>
       <c r="E29" t="n">
-        <v>1.254257388269117</v>
+        <v>5.180402521229112</v>
       </c>
     </row>
     <row r="30">
@@ -11624,16 +11624,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.71300723838514</v>
+        <v>0.4292506686180419</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.1821925454415482</v>
       </c>
       <c r="D30" t="n">
-        <v>3.47156130253205</v>
+        <v>1.177616160407668</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.061219928201807</v>
+        <v>-0.4624658070771426</v>
       </c>
     </row>
     <row r="31">
@@ -11643,16 +11643,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-5.69586399712785</v>
+        <v>-0.7051532874844841</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.1923082850250455</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.1226031581915133</v>
+        <v>0.3763124036186479</v>
       </c>
       <c r="E31" t="n">
-        <v>2.082383072138545</v>
+        <v>0.9833953420184738</v>
       </c>
     </row>
     <row r="33">
@@ -11915,16 +11915,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6.06246581258421</v>
+        <v>3.90156129586136</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.03715565195155966</v>
       </c>
       <c r="D12" t="n">
-        <v>0.01703880609544329</v>
+        <v>0.03126864952327872</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.6155865281526118</v>
+        <v>0.06217640973751559</v>
       </c>
     </row>
     <row r="13">
@@ -11934,16 +11934,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.9694976666154584</v>
+        <v>-0.4056501214312176</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0.7283863404946835</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1464482608368426</v>
+        <v>0.1275358456358952</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5896705978039853</v>
+        <v>0.01006394370937958</v>
       </c>
     </row>
     <row r="14">
@@ -11953,16 +11953,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2061286424885806</v>
+        <v>0.09869829688761507</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>-0.03347881825868047</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8581938032910172</v>
+        <v>0.6683099264886546</v>
       </c>
       <c r="E14" t="n">
-        <v>0.05360641798218049</v>
+        <v>0.191256950796127</v>
       </c>
     </row>
     <row r="15">
@@ -11972,16 +11972,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-4.299096788457331</v>
+        <v>-2.594609471317757</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>0.2679368258124373</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.02168087022330316</v>
+        <v>0.1728855783521715</v>
       </c>
       <c r="E15" t="n">
-        <v>0.972309512366446</v>
+        <v>0.7365026957569778</v>
       </c>
     </row>
     <row r="17">
@@ -12125,16 +12125,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>6.06246581258421</v>
+        <v>3.90156129586136</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.08108112587151514</v>
       </c>
       <c r="D28" t="n">
-        <v>0.418737673477745</v>
+        <v>0.7684436034324208</v>
       </c>
       <c r="E28" t="n">
-        <v>-415.790295746999</v>
+        <v>41.99628583626032</v>
       </c>
     </row>
     <row r="29">
@@ -12144,16 +12144,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.208089767587319</v>
+        <v>-0.5054800829303959</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>0.7283863404946835</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4184973736346616</v>
+        <v>0.364452374769823</v>
       </c>
       <c r="E29" t="n">
-        <v>37.89131268620707</v>
+        <v>0.6466933222864361</v>
       </c>
     </row>
     <row r="30">
@@ -12163,16 +12163,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.4135264401175668</v>
+        <v>0.1980042892867898</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>-0.05223407980395586</v>
       </c>
       <c r="D30" t="n">
-        <v>0.8581938032910172</v>
+        <v>0.6683099264886546</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1689831226599105</v>
+        <v>0.6028978990292868</v>
       </c>
     </row>
     <row r="31">
@@ -12182,16 +12182,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-17.29897742014015</v>
+        <v>-10.44035360611494</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.7257742859381869</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.03553421512279587</v>
+        <v>0.2833536324659151</v>
       </c>
       <c r="E31" t="n">
-        <v>0.972309512366446</v>
+        <v>0.7365026957569778</v>
       </c>
     </row>
     <row r="33">
@@ -12460,10 +12460,10 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>0.02703377860253493</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>0.04103478545678905</v>
       </c>
     </row>
     <row r="13">
@@ -12479,10 +12479,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>0.1636384962761097</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>0.06541906636801165</v>
       </c>
     </row>
     <row r="14">
@@ -12498,10 +12498,10 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0.515715565657445</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>0.2374575664478062</v>
       </c>
     </row>
     <row r="15">
@@ -12517,10 +12517,10 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>0.2936121594639105</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0.6560885817273927</v>
       </c>
     </row>
     <row r="17">
@@ -12559,16 +12559,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.3273201979128418</v>
+        <v>0.3275643340839757</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1836620239089209</v>
+        <v>0.1836465444807249</v>
       </c>
       <c r="D20" t="n">
         <v>0.0476319459668316</v>
       </c>
       <c r="E20" t="n">
-        <v>0.05039196796156638</v>
+        <v>0.05044357209849645</v>
       </c>
     </row>
     <row r="21">
@@ -12578,16 +12578,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2836721121423696</v>
+        <v>0.2833596177192036</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3812073892364156</v>
+        <v>0.377345430368541</v>
       </c>
       <c r="D21" t="n">
         <v>0.1727025437468194</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0723585929363406</v>
+        <v>0.07531775899468374</v>
       </c>
     </row>
     <row r="22">
@@ -12597,16 +12597,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2351665299796667</v>
+        <v>0.2351570199628868</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2717524605038541</v>
+        <v>0.2752747603791644</v>
       </c>
       <c r="D22" t="n">
         <v>0.4813219335538785</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2427607211746757</v>
+        <v>0.2459815582917445</v>
       </c>
     </row>
     <row r="23">
@@ -12616,16 +12616,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1538411599651218</v>
+        <v>0.1539190282339336</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1633781263508093</v>
+        <v>0.1637332647715697</v>
       </c>
       <c r="D23" t="n">
         <v>0.2983435767324707</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6344887179274177</v>
+        <v>0.6282571106150756</v>
       </c>
     </row>
     <row r="25">
@@ -12670,10 +12670,10 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>0.5313763600106899</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>5.739324859985421</v>
       </c>
     </row>
     <row r="29">
@@ -12689,10 +12689,10 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>0.4319441562211248</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>3.036105350078781</v>
       </c>
     </row>
     <row r="30">
@@ -12708,10 +12708,10 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0.515715565657445</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>0.8850539303372158</v>
       </c>
     </row>
     <row r="31">
@@ -12727,10 +12727,10 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>0.5277569970521719</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0.6560885817273927</v>
       </c>
     </row>
     <row r="33">
@@ -12769,16 +12769,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.3273201979128418</v>
+        <v>0.3275643340839757</v>
       </c>
       <c r="C36" t="n">
-        <v>0.4276254428172073</v>
+        <v>0.4275894016302707</v>
       </c>
       <c r="D36" t="n">
         <v>0.9362542484426314</v>
       </c>
       <c r="E36" t="n">
-        <v>7.048065957843508</v>
+        <v>7.055283563654381</v>
       </c>
     </row>
     <row r="37">
@@ -12788,16 +12788,16 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.3613129248460191</v>
+        <v>0.3609149009684534</v>
       </c>
       <c r="C37" t="n">
-        <v>0.3812073892364156</v>
+        <v>0.377345430368541</v>
       </c>
       <c r="D37" t="n">
         <v>0.4558698364600696</v>
       </c>
       <c r="E37" t="n">
-        <v>3.358169465494218</v>
+        <v>3.4955046553755</v>
       </c>
     </row>
     <row r="38">
@@ -12807,16 +12807,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4861971346573276</v>
+        <v>0.4861774730885264</v>
       </c>
       <c r="C38" t="n">
-        <v>0.4201344345865717</v>
+        <v>0.4255799766943196</v>
       </c>
       <c r="D38" t="n">
         <v>0.4813219335538785</v>
       </c>
       <c r="E38" t="n">
-        <v>0.9048198952816677</v>
+        <v>0.9168246277148382</v>
       </c>
     </row>
     <row r="39">
@@ -12826,16 +12826,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.687922812284321</v>
+        <v>0.6882710114169908</v>
       </c>
       <c r="C39" t="n">
-        <v>0.5027317264184215</v>
+        <v>0.5038245247958678</v>
       </c>
       <c r="D39" t="n">
         <v>0.5362615445954867</v>
       </c>
       <c r="E39" t="n">
-        <v>0.6344887179274177</v>
+        <v>0.6282571106150756</v>
       </c>
     </row>
   </sheetData>
@@ -12993,16 +12993,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.483778246559456</v>
+        <v>1.053852038475631</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.07773536716053982</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3647677058329173</v>
+        <v>-1.383914553998055</v>
       </c>
       <c r="E12" t="n">
-        <v>0.04442464622266368</v>
+        <v>0.05341804535904035</v>
       </c>
     </row>
     <row r="13">
@@ -13012,16 +13012,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5393411371500731</v>
+        <v>0.01364201936531988</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0.6632641778795503</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.07010609945039255</v>
+        <v>-0.9037339441317345</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.245881413569248</v>
+        <v>0.05099741271090497</v>
       </c>
     </row>
     <row r="14">
@@ -13031,16 +13031,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.2446495667044788</v>
+        <v>0.04203251689246861</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.01894501290182522</v>
       </c>
       <c r="D14" t="n">
-        <v>1.245265161242544</v>
+        <v>2.974783727187137</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.5733284789689467</v>
+        <v>0.2065239243379032</v>
       </c>
     </row>
     <row r="15">
@@ -13050,16 +13050,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.7784698170050504</v>
+        <v>-0.1095265747334192</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>0.2400554420580847</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1896086440407653</v>
+        <v>0.3128647709426525</v>
       </c>
       <c r="E15" t="n">
-        <v>1.774785246315531</v>
+        <v>0.6890606175921516</v>
       </c>
     </row>
     <row r="17">
@@ -13203,16 +13203,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.483778246559456</v>
+        <v>1.053852038475631</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.179067852754894</v>
       </c>
       <c r="D28" t="n">
-        <v>-10.04759387027511</v>
+        <v>-38.12018215259603</v>
       </c>
       <c r="E28" t="n">
-        <v>12.32253815919811</v>
+        <v>14.81713324237436</v>
       </c>
     </row>
     <row r="29">
@@ -13222,16 +13222,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6846486730390462</v>
+        <v>0.01731740787545444</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>0.6632641778795503</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.1941850363695752</v>
+        <v>-2.503228822961678</v>
       </c>
       <c r="E29" t="n">
-        <v>-11.66100109358585</v>
+        <v>2.418567864725696</v>
       </c>
     </row>
     <row r="30">
@@ -13241,16 +13241,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.4861681891471332</v>
+        <v>0.0835271155317098</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.0290703878108722</v>
       </c>
       <c r="D30" t="n">
-        <v>1.245265161242544</v>
+        <v>2.974783727187137</v>
       </c>
       <c r="E30" t="n">
-        <v>-2.023033297918357</v>
+        <v>0.7287354301738415</v>
       </c>
     </row>
     <row r="31">
@@ -13260,16 +13260,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-3.271620351736613</v>
+        <v>-0.4602996328520862</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.7046528440352734</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3161857055527802</v>
+        <v>0.5217239374479323</v>
       </c>
       <c r="E31" t="n">
-        <v>1.774785246315531</v>
+        <v>0.6890606175921516</v>
       </c>
     </row>
     <row r="33">
@@ -13532,16 +13532,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.874274661508704</v>
+        <v>0.671327486924822</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.03312170579779606</v>
+        <v>0.2592396433661347</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3447913682803398</v>
+        <v>0.05056980889994748</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.2636899632740317</v>
+        <v>0.04858923161062735</v>
       </c>
     </row>
     <row r="13">
@@ -13551,16 +13551,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6063085850319895</v>
+        <v>0.06281980856511192</v>
       </c>
       <c r="C13" t="n">
-        <v>1.35361763296598</v>
+        <v>0.850616500628945</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1074190776281868</v>
+        <v>0.05007686419336492</v>
       </c>
       <c r="E13" t="n">
-        <v>0.01640990641634186</v>
+        <v>0.0514311850623459</v>
       </c>
     </row>
     <row r="14">
@@ -13570,16 +13570,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.4129593810444875</v>
+        <v>0.1231193409483819</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.2995028749401054</v>
+        <v>-0.09225829170109912</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9989735510359975</v>
+        <v>0.6599398879048071</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2650520151388027</v>
+        <v>0.2160594576437755</v>
       </c>
     </row>
     <row r="15">
@@ -13589,16 +13589,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-1.067623865496206</v>
+        <v>0.1427333635616842</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.02099305222807856</v>
+        <v>-0.01759785229398059</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.451183996944524</v>
+        <v>0.2394134390018805</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9822280417188871</v>
+        <v>0.6839201256832511</v>
       </c>
     </row>
     <row r="17">
@@ -13637,7 +13637,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.3846523413832473</v>
+        <v>0.3929771122588974</v>
       </c>
       <c r="C20" t="n">
         <v>0.1932608720752369</v>
@@ -13656,7 +13656,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2799479165880693</v>
+        <v>0.286989747283611</v>
       </c>
       <c r="C21" t="n">
         <v>0.3789883281445952</v>
@@ -13675,7 +13675,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.19445800300004</v>
+        <v>0.1981645666240107</v>
       </c>
       <c r="C22" t="n">
         <v>0.2636027363571242</v>
@@ -13694,7 +13694,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1409417390286436</v>
+        <v>0.1218685738334811</v>
       </c>
       <c r="C23" t="n">
         <v>0.1641480634230438</v>
@@ -13742,16 +13742,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.874274661508704</v>
+        <v>0.671327486924822</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.07262771555303063</v>
+        <v>0.5684484728355254</v>
       </c>
       <c r="D28" t="n">
-        <v>8.930892061199815</v>
+        <v>1.30987474278568</v>
       </c>
       <c r="E28" t="n">
-        <v>-112.9203424108536</v>
+        <v>20.80743841300632</v>
       </c>
     </row>
     <row r="29">
@@ -13761,16 +13761,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7663941407341962</v>
+        <v>0.07940631947971755</v>
       </c>
       <c r="C29" t="n">
-        <v>1.35361763296598</v>
+        <v>0.850616500628945</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3203782881612829</v>
+        <v>0.1493546619557406</v>
       </c>
       <c r="E29" t="n">
-        <v>1.653704625984746</v>
+        <v>5.182966099841963</v>
       </c>
     </row>
     <row r="30">
@@ -13780,16 +13780,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.8538760350009083</v>
+        <v>0.2545738382671683</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.4646571653971113</v>
+        <v>-0.1431321028714178</v>
       </c>
       <c r="D30" t="n">
-        <v>0.9989735510359975</v>
+        <v>0.6599398879048071</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9140002012681709</v>
+        <v>0.7450552212134173</v>
       </c>
     </row>
     <row r="31">
@@ -13799,16 +13799,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-4.574766264926502</v>
+        <v>0.6116121956471972</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.06144156264687549</v>
+        <v>-0.05150463745928731</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7357337471746782</v>
+        <v>0.3904051291572911</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9822280417188871</v>
+        <v>0.6839201256832511</v>
       </c>
     </row>
     <row r="33">
@@ -13847,7 +13847,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.3846523413832473</v>
+        <v>0.3929771122588974</v>
       </c>
       <c r="C36" t="n">
         <v>0.4237733325179441</v>
@@ -13866,7 +13866,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.3538634422808345</v>
+        <v>0.3627645496019862</v>
       </c>
       <c r="C37" t="n">
         <v>0.3789883281445952</v>
@@ -13885,7 +13885,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4020807764577246</v>
+        <v>0.409744837370228</v>
       </c>
       <c r="C38" t="n">
         <v>0.4089606829020186</v>
@@ -13904,7 +13904,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.603935087877262</v>
+        <v>0.5222066107233296</v>
       </c>
       <c r="C39" t="n">
         <v>0.4804214943399557</v>
@@ -14071,16 +14071,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9123789168498982</v>
+        <v>1.194606990052342</v>
       </c>
       <c r="C12" t="n">
-        <v>0.08608484484985579</v>
+        <v>0.3642648288039005</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5264583403866339</v>
+        <v>0.1561971089392329</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1230737344968297</v>
+        <v>0.04937510705101881</v>
       </c>
     </row>
     <row r="13">
@@ -14090,16 +14090,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.06645573828603168</v>
+        <v>0.03670227553835027</v>
       </c>
       <c r="C13" t="n">
-        <v>1.325020161169967</v>
+        <v>0.9146347050738465</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.07617564410739076</v>
+        <v>0.1351953507660121</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.01233931341024516</v>
+        <v>0.05188365936798123</v>
       </c>
     </row>
     <row r="14">
@@ -14109,16 +14109,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.2786655081860867</v>
+        <v>-0.2772410994217605</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.3680424052851897</v>
+        <v>-0.196474018003136</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8410806784710704</v>
+        <v>0.5566758540835121</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.4464240665051384</v>
+        <v>0.219432507774486</v>
       </c>
     </row>
     <row r="15">
@@ -14128,16 +14128,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4327423296222201</v>
+        <v>0.04593183383106812</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.04306260073463364</v>
+        <v>-0.08242551587461086</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2913633747503135</v>
+        <v>0.151931686211243</v>
       </c>
       <c r="E15" t="n">
-        <v>1.335689645418554</v>
+        <v>0.6793087258065144</v>
       </c>
     </row>
     <row r="17">
@@ -14176,7 +14176,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2687761592624662</v>
+        <v>0.2688330938793855</v>
       </c>
       <c r="C20" t="n">
         <v>-7.778608825729308</v>
@@ -14195,7 +14195,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.3336918834724372</v>
+        <v>0.3337371916420269</v>
       </c>
       <c r="C21" t="n">
         <v>13.53777112939428</v>
@@ -14214,7 +14214,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2326463637759661</v>
+        <v>0.2325554532049632</v>
       </c>
       <c r="C22" t="n">
         <v>-5.540014958863176</v>
@@ -14233,7 +14233,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1648855934891305</v>
+        <v>0.1648742612736244</v>
       </c>
       <c r="C23" t="n">
         <v>0.7808526551982069</v>
@@ -14281,16 +14281,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.9123789168498982</v>
+        <v>1.194606990052342</v>
       </c>
       <c r="C28" t="n">
-        <v>0.2173486456414053</v>
+        <v>0.9197027343595051</v>
       </c>
       <c r="D28" t="n">
-        <v>15.76092355774746</v>
+        <v>4.676173792069541</v>
       </c>
       <c r="E28" t="n">
-        <v>32.0694557748342</v>
+        <v>12.86572491217564</v>
       </c>
     </row>
     <row r="29">
@@ -14300,16 +14300,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.08569716219056234</v>
+        <v>0.04732895820124863</v>
       </c>
       <c r="C29" t="n">
-        <v>1.325020161169967</v>
+        <v>0.9146347050738465</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.2059120105817568</v>
+        <v>0.3654494402212012</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.6822068902036914</v>
+        <v>2.868505623694572</v>
       </c>
     </row>
     <row r="30">
@@ -14319,16 +14319,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.5774743083080599</v>
+        <v>-0.5745225276184386</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.5828433470213187</v>
+        <v>-0.3111423374351118</v>
       </c>
       <c r="D30" t="n">
-        <v>0.8410806784710704</v>
+        <v>0.5566758540835121</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.479139055674847</v>
+        <v>0.7270468074780214</v>
       </c>
     </row>
     <row r="31">
@@ -14338,16 +14338,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.783642932070043</v>
+        <v>0.1893181811941552</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1246150560004435</v>
+        <v>-0.2385239186986476</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.4807136234446207</v>
+        <v>0.2506685387524986</v>
       </c>
       <c r="E31" t="n">
-        <v>1.335689645418554</v>
+        <v>0.6793087258065144</v>
       </c>
     </row>
     <row r="33">
@@ -14386,7 +14386,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.2687761592624662</v>
+        <v>0.2688330938793855</v>
       </c>
       <c r="C36" t="n">
         <v>-19.63957879224056</v>
@@ -14405,7 +14405,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.4303081749920512</v>
+        <v>0.4303666015727804</v>
       </c>
       <c r="C37" t="n">
         <v>13.53777112939428</v>
@@ -14424,7 +14424,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4821095329537417</v>
+        <v>0.4819211403555707</v>
       </c>
       <c r="C38" t="n">
         <v>-8.773339198970621</v>
@@ -14443,7 +14443,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6796123311620698</v>
+        <v>0.6795656229370857</v>
       </c>
       <c r="C39" t="n">
         <v>2.259640516262641</v>
@@ -14610,16 +14610,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>0.6652849546407601</v>
       </c>
       <c r="C12" t="n">
-        <v>0.09280180761781798</v>
+        <v>0.3157389775818319</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4206763730326972</v>
+        <v>0.1032468005691869</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.3197894609850865</v>
+        <v>0.02744616852804313</v>
       </c>
     </row>
     <row r="13">
@@ -14629,16 +14629,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.3471272074759496</v>
       </c>
       <c r="C13" t="n">
-        <v>1.622014202711427</v>
+        <v>0.8987025252124919</v>
       </c>
       <c r="D13" t="n">
-        <v>0.01751256002347462</v>
+        <v>-0.259138324339313</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.3645776437028829</v>
+        <v>0.06138408484692284</v>
       </c>
     </row>
     <row r="14">
@@ -14648,16 +14648,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>-0.06772353244827373</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.210377663008393</v>
+        <v>-0.07575651513639345</v>
       </c>
       <c r="D14" t="n">
-        <v>1.414857228286654</v>
+        <v>1.19440733148789</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.4254743977181616</v>
+        <v>0.1996550417017031</v>
       </c>
     </row>
     <row r="15">
@@ -14667,16 +14667,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>0.05531137033156421</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.5044383473208522</v>
+        <v>-0.1386849876579304</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.8530461613428257</v>
+        <v>-0.03851580771776417</v>
       </c>
       <c r="E15" t="n">
-        <v>2.109841502406131</v>
+        <v>0.711514704923331</v>
       </c>
     </row>
     <row r="17">
@@ -14820,16 +14820,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>0.6652849546407601</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1951364984058173</v>
+        <v>0.6639116206581516</v>
       </c>
       <c r="D28" t="n">
-        <v>9.943015177332843</v>
+        <v>2.440318902793932</v>
       </c>
       <c r="E28" t="n">
-        <v>-78.07695432016695</v>
+        <v>6.70101272201576</v>
       </c>
     </row>
     <row r="29">
@@ -14839,16 +14839,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.45360972611109</v>
       </c>
       <c r="C29" t="n">
-        <v>1.622014202711427</v>
+        <v>0.8987025252124919</v>
       </c>
       <c r="D29" t="n">
-        <v>0.04760001199296313</v>
+        <v>-0.7043508961484385</v>
       </c>
       <c r="E29" t="n">
-        <v>-18.27139336651139</v>
+        <v>3.076361867091</v>
       </c>
     </row>
     <row r="30">
@@ -14858,16 +14858,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>-0.1276188087289438</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.2997267888462176</v>
+        <v>-0.1079309309330298</v>
       </c>
       <c r="D30" t="n">
-        <v>1.414857228286654</v>
+        <v>1.19440733148789</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.604271150223917</v>
+        <v>0.752808688646328</v>
       </c>
     </row>
     <row r="31">
@@ -14877,16 +14877,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.2186208401238037</v>
       </c>
       <c r="C31" t="n">
-        <v>-1.429151078505205</v>
+        <v>-0.3929158057401695</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.42701906198108</v>
+        <v>-0.06443120465406887</v>
       </c>
       <c r="E31" t="n">
-        <v>2.109841502406131</v>
+        <v>0.711514704923331</v>
       </c>
     </row>
     <row r="33">
@@ -15149,16 +15149,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.095023174975477</v>
+        <v>0.6605114777002352</v>
       </c>
       <c r="C12" t="n">
-        <v>1.086240896290777</v>
+        <v>0.5122202028864675</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>0.04173022244878854</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.2353534988570983</v>
+        <v>0.02009545242291587</v>
       </c>
     </row>
     <row r="13">
@@ -15168,16 +15168,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5192225288641297</v>
+        <v>0.2540036560062533</v>
       </c>
       <c r="C13" t="n">
-        <v>4.742629695431754</v>
+        <v>1.740920468250493</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>0.1287152427085564</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1781006580792393</v>
+        <v>0.05735599861077729</v>
       </c>
     </row>
     <row r="14">
@@ -15187,16 +15187,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.2257422831279388</v>
+        <v>0.03579987652247673</v>
       </c>
       <c r="C14" t="n">
-        <v>-2.955851150893397</v>
+        <v>-0.9232371603118332</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0.5780632479824205</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1331570175791863</v>
+        <v>0.2407256691403885</v>
       </c>
     </row>
     <row r="15">
@@ -15206,16 +15206,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.3885034207116677</v>
+        <v>0.04968498977103473</v>
       </c>
       <c r="C15" t="n">
-        <v>-1.873019440829135</v>
+        <v>-0.3299035108251269</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>0.2514912868602345</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9240958231986727</v>
+        <v>0.6818228798259184</v>
       </c>
     </row>
     <row r="17">
@@ -15359,16 +15359,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.095023174975477</v>
+        <v>0.6605114777002352</v>
       </c>
       <c r="C28" t="n">
-        <v>2.313054905388703</v>
+        <v>1.090728085244713</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>1.069389522785599</v>
       </c>
       <c r="E28" t="n">
-        <v>-58.71072467964986</v>
+        <v>5.012963819293706</v>
       </c>
     </row>
     <row r="29">
@@ -15378,16 +15378,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6619982491439566</v>
+        <v>0.3238495369608761</v>
       </c>
       <c r="C29" t="n">
-        <v>4.742629695431754</v>
+        <v>1.740920468250493</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>0.3946972225793906</v>
       </c>
       <c r="E29" t="n">
-        <v>14.32183857357196</v>
+        <v>4.612242100554727</v>
       </c>
     </row>
     <row r="30">
@@ -15397,16 +15397,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.461250176515635</v>
+        <v>0.0731484555592618</v>
       </c>
       <c r="C30" t="n">
-        <v>-4.4957849062011</v>
+        <v>-1.404223514069501</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0.5780632479824205</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4038762368966318</v>
+        <v>0.7301408453296621</v>
       </c>
     </row>
     <row r="31">
@@ -15416,16 +15416,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-1.572984036752607</v>
+        <v>0.2011660428443354</v>
       </c>
       <c r="C31" t="n">
-        <v>-5.235998048999025</v>
+        <v>-0.9222403683507054</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>0.4200436379591284</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9240958231986727</v>
+        <v>0.6818228798259184</v>
       </c>
     </row>
     <row r="33">
@@ -15688,16 +15688,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.184426229508197</v>
+        <v>0.935015615080826</v>
       </c>
       <c r="C12" t="n">
-        <v>0.161489644885709</v>
+        <v>-0.03242925344536406</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3143322314378558</v>
+        <v>0.0128670733378121</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.3504654555309577</v>
+        <v>0.0335057541468782</v>
       </c>
     </row>
     <row r="13">
@@ -15707,16 +15707,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2418032786885246</v>
+        <v>0.06809181998796071</v>
       </c>
       <c r="C13" t="n">
-        <v>1.289291754594475</v>
+        <v>1.045783450261403</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.2817842690125849</v>
+        <v>0.1391464439361067</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1467920322068794</v>
+        <v>0.05917496633348193</v>
       </c>
     </row>
     <row r="14">
@@ -15726,16 +15726,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.6065573770491803</v>
+        <v>-0.04230294765610745</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.4947507040043872</v>
+        <v>-0.06022707948789228</v>
       </c>
       <c r="D14" t="n">
-        <v>1.505120938282301</v>
+        <v>0.5728043304575295</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2305030000226507</v>
+        <v>0.2357818486055558</v>
       </c>
     </row>
     <row r="15">
@@ -15745,16 +15745,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.819672131147541</v>
+        <v>0.03919551258732074</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0439693045242029</v>
+        <v>0.04687288267185349</v>
       </c>
       <c r="D15" t="n">
-        <v>0.09099556216813942</v>
+        <v>0.2751821522685517</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9731704233014277</v>
+        <v>0.6715374309140842</v>
       </c>
     </row>
     <row r="17">
@@ -15793,10 +15793,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.3273551045282128</v>
+        <v>0.3265966077319715</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1016040125148909</v>
+        <v>0.1017541118782022</v>
       </c>
       <c r="D20" t="n">
         <v>-8.576923076923077</v>
@@ -15812,10 +15812,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2765050295511051</v>
+        <v>0.2788039044156225</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3068768483047205</v>
+        <v>0.3072867921682494</v>
       </c>
       <c r="D21" t="n">
         <v>-14.84615384615385</v>
@@ -15831,10 +15831,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2378404897685158</v>
+        <v>0.2364899261012149</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3745044825903295</v>
+        <v>0.374284159404064</v>
       </c>
       <c r="D22" t="n">
         <v>21.07692307692308</v>
@@ -15850,10 +15850,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1582993761521662</v>
+        <v>0.1581095617511909</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2170146565900591</v>
+        <v>0.2166749365494844</v>
       </c>
       <c r="D23" t="n">
         <v>3.346153846153846</v>
@@ -15898,16 +15898,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.184426229508197</v>
+        <v>0.935015615080826</v>
       </c>
       <c r="C28" t="n">
-        <v>0.3916948834279739</v>
+        <v>-0.07865750560618262</v>
       </c>
       <c r="D28" t="n">
-        <v>-9.634993484573622</v>
+        <v>0.3944048855831717</v>
       </c>
       <c r="E28" t="n">
-        <v>-406.5252721927295</v>
+        <v>38.86527362289249</v>
       </c>
     </row>
     <row r="29">
@@ -15917,16 +15917,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.2830904330176356</v>
+        <v>0.0797182855000944</v>
       </c>
       <c r="C29" t="n">
-        <v>1.289291754594475</v>
+        <v>1.045783450261403</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.9221289618776066</v>
+        <v>0.4553517708613896</v>
       </c>
       <c r="E29" t="n">
-        <v>16.91581513391227</v>
+        <v>6.819122100863943</v>
       </c>
     </row>
     <row r="30">
@@ -15936,16 +15936,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-1.171538621781102</v>
+        <v>-0.08170626369332888</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.7685949393102863</v>
+        <v>-0.09356273397727573</v>
       </c>
       <c r="D30" t="n">
-        <v>1.505120938282301</v>
+        <v>0.5728043304575295</v>
       </c>
       <c r="E30" t="n">
-        <v>0.6487267433095653</v>
+        <v>0.6635835141510547</v>
       </c>
     </row>
     <row r="31">
@@ -15955,16 +15955,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-3.087930602692886</v>
+        <v>0.1476602878240788</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1221526869214424</v>
+        <v>0.1302192205239166</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1524783426968211</v>
+        <v>0.4611138996000884</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9731704233014277</v>
+        <v>0.6715374309140842</v>
       </c>
     </row>
     <row r="33">
@@ -16003,10 +16003,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.3273551045282128</v>
+        <v>0.3265966077319715</v>
       </c>
       <c r="C36" t="n">
-        <v>0.246441633245281</v>
+        <v>0.2468057008773354</v>
       </c>
       <c r="D36" t="n">
         <v>-262.9020816154542</v>
@@ -16022,10 +16022,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.3237173994154418</v>
+        <v>0.3264087999803112</v>
       </c>
       <c r="C37" t="n">
-        <v>0.3068768483047205</v>
+        <v>0.3072867921682494</v>
       </c>
       <c r="D37" t="n">
         <v>-48.5835085187728</v>
@@ -16041,10 +16041,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4593783376977327</v>
+        <v>0.4567697839857744</v>
       </c>
       <c r="C38" t="n">
-        <v>0.5817925022404657</v>
+        <v>0.5814502302950076</v>
       </c>
       <c r="D38" t="n">
         <v>21.07692307692308</v>
@@ -16060,10 +16060,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.596357335369109</v>
+        <v>0.595642252258033</v>
       </c>
       <c r="C39" t="n">
-        <v>0.6028961269837233</v>
+        <v>0.6019523386703464</v>
       </c>
       <c r="D39" t="n">
         <v>5.607042593213142</v>
@@ -16227,16 +16227,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>0.6084610745972517</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.2383089682299795</v>
       </c>
       <c r="D12" t="n">
-        <v>0.09036144578313253</v>
+        <v>0.06184539534528455</v>
       </c>
       <c r="E12" t="n">
-        <v>0.07011070110701106</v>
+        <v>0.05206658161527761</v>
       </c>
     </row>
     <row r="13">
@@ -16246,16 +16246,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.07086748426399275</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0.6387252363430718</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2048192771084337</v>
+        <v>0.1512785996131272</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2878228782287823</v>
+        <v>0.06360982008999755</v>
       </c>
     </row>
     <row r="14">
@@ -16265,16 +16265,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>-0.0001841971760144316</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.04150293053366573</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8385542168674699</v>
+        <v>0.552871630677227</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.1642066420664207</v>
+        <v>0.2102608290870899</v>
       </c>
     </row>
     <row r="15">
@@ -16284,16 +16284,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>0.32085563831477</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>0.08146286489328293</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1337349397590361</v>
+        <v>0.2340043743643614</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8062730627306273</v>
+        <v>0.6740627692076349</v>
       </c>
     </row>
     <row r="17">
@@ -16332,7 +16332,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.3150292366749644</v>
+        <v>0.3139423396879463</v>
       </c>
       <c r="C20" t="n">
         <v>0.1890975036361414</v>
@@ -16351,7 +16351,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2496393655283955</v>
+        <v>0.2497283869056641</v>
       </c>
       <c r="C21" t="n">
         <v>0.3907091072427731</v>
@@ -16370,7 +16370,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2682303220159779</v>
+        <v>0.2679674296207664</v>
       </c>
       <c r="C22" t="n">
         <v>0.2590738815897367</v>
@@ -16389,7 +16389,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1671010757806621</v>
+        <v>0.1683618437856232</v>
       </c>
       <c r="C23" t="n">
         <v>0.1611195075313488</v>
@@ -16437,16 +16437,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>0.6084610745972517</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.5620948556237102</v>
       </c>
       <c r="D28" t="n">
-        <v>1.861814175284104</v>
+        <v>1.27426727994423</v>
       </c>
       <c r="E28" t="n">
-        <v>14.05923100075644</v>
+        <v>10.44086119223995</v>
       </c>
     </row>
     <row r="29">
@@ -16456,16 +16456,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.0898538370777958</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>0.6387252363430718</v>
       </c>
       <c r="D29" t="n">
-        <v>0.542915787475711</v>
+        <v>0.4009951660638971</v>
       </c>
       <c r="E29" t="n">
-        <v>19.9120590596523</v>
+        <v>4.400631743384562</v>
       </c>
     </row>
     <row r="30">
@@ -16475,16 +16475,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>-0.0003800221507626397</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.06452151106092022</v>
       </c>
       <c r="D30" t="n">
-        <v>0.8385542168674699</v>
+        <v>0.552871630677227</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.6286721463884782</v>
+        <v>0.8049925694853052</v>
       </c>
     </row>
     <row r="31">
@@ -16494,16 +16494,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>1.41977833308458</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.2477841853198729</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.2397672505186127</v>
+        <v>0.4195357290455585</v>
       </c>
       <c r="E31" t="n">
-        <v>0.8062730627306273</v>
+        <v>0.6740627692076349</v>
       </c>
     </row>
     <row r="33">
@@ -16542,7 +16542,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.3150292366749644</v>
+        <v>0.3139423396879463</v>
       </c>
       <c r="C36" t="n">
         <v>0.4460207049471395</v>
@@ -16561,7 +16561,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.3165211113581157</v>
+        <v>0.3166339827604606</v>
       </c>
       <c r="C37" t="n">
         <v>0.3907091072427731</v>
@@ -16580,7 +16580,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5533931956930818</v>
+        <v>0.5528508153178278</v>
       </c>
       <c r="C38" t="n">
         <v>0.4027628435304931</v>
@@ -16599,7 +16599,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7394181634912143</v>
+        <v>0.7449970310027582</v>
       </c>
       <c r="C39" t="n">
         <v>0.490074415687365</v>
@@ -16766,16 +16766,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>1.054627267447814</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.03703703703703703</v>
+        <v>0.02332032445668809</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.660194174757281</v>
+        <v>-0.00495418081243993</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>0.04600050167606681</v>
       </c>
     </row>
     <row r="13">
@@ -16785,16 +16785,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.06708279719161903</v>
       </c>
       <c r="C13" t="n">
-        <v>1.707818930041152</v>
+        <v>1.144715250144543</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.3592233009708738</v>
+        <v>0.135245334575627</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>0.05947448798016649</v>
       </c>
     </row>
     <row r="14">
@@ -16804,16 +16804,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>-0.2829382865027485</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1193415637860082</v>
+        <v>0.2239269802401116</v>
       </c>
       <c r="D14" t="n">
-        <v>4.601941747572815</v>
+        <v>0.6309352406728866</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>0.2203217900553055</v>
       </c>
     </row>
     <row r="15">
@@ -16823,16 +16823,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>0.1612282218633156</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.7901234567901234</v>
+        <v>-0.3919625548413427</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.58252427184466</v>
+        <v>0.238773605563926</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0.6742032202884608</v>
       </c>
     </row>
     <row r="17">
@@ -16871,13 +16871,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.3048289592768349</v>
+        <v>0.2907385182434665</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1003390764025002</v>
+        <v>0.09574872543236068</v>
       </c>
       <c r="D20" t="n">
-        <v>0.07702781268134576</v>
+        <v>1.511627906976744</v>
       </c>
       <c r="E20" t="n">
         <v>0.04439794421008626</v>
@@ -16890,13 +16890,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2400687793513263</v>
+        <v>0.2880761245950466</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2923645782687812</v>
+        <v>0.2824318289669617</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6198118269513162</v>
+        <v>-5.511627906976744</v>
       </c>
       <c r="E21" t="n">
         <v>0.06892603219349301</v>
@@ -16909,13 +16909,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2972297199018927</v>
+        <v>0.2323700195288486</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3972012732605019</v>
+        <v>0.4110841377947566</v>
       </c>
       <c r="D22" t="n">
-        <v>2.129795750278479</v>
+        <v>9.302325581395349</v>
       </c>
       <c r="E22" t="n">
         <v>0.2254081096326985</v>
@@ -16928,13 +16928,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1578725414699463</v>
+        <v>0.1888153376326384</v>
       </c>
       <c r="C23" t="n">
-        <v>0.210095072068217</v>
+        <v>0.2107353078059213</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.5870117360085079</v>
+        <v>-4.302325581395348</v>
       </c>
       <c r="E23" t="n">
         <v>0.6612679139637218</v>
@@ -16976,16 +16976,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>1.054627267447814</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.08453371860098632</v>
+        <v>0.05322655112324501</v>
       </c>
       <c r="D28" t="n">
-        <v>-31.57646310080269</v>
+        <v>-0.09422723558320209</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>10.42319445660607</v>
       </c>
     </row>
     <row r="29">
@@ -16995,16 +16995,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.0859420136992525</v>
       </c>
       <c r="C29" t="n">
-        <v>1.707818930041152</v>
+        <v>1.144715250144543</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.9213232457180751</v>
+        <v>0.3468724614541269</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>4.331218907569189</v>
       </c>
     </row>
     <row r="30">
@@ -17014,16 +17014,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>-0.5979818354102024</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1884083928176306</v>
+        <v>0.3535207778171507</v>
       </c>
       <c r="D30" t="n">
-        <v>4.601941747572815</v>
+        <v>0.6309352406728866</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>0.8359806517083033</v>
       </c>
     </row>
     <row r="31">
@@ -17033,16 +17033,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.7397138669984085</v>
       </c>
       <c r="C31" t="n">
-        <v>-2.48537266958617</v>
+        <v>-1.232937730087677</v>
       </c>
       <c r="D31" t="n">
-        <v>-2.860631607673134</v>
+        <v>0.4316163330361177</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0.6742032202884608</v>
       </c>
     </row>
     <row r="33">
@@ -17081,13 +17081,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.3048289592768349</v>
+        <v>0.2907385182434665</v>
       </c>
       <c r="C36" t="n">
-        <v>0.2290149517308791</v>
+        <v>0.2185378869267616</v>
       </c>
       <c r="D36" t="n">
-        <v>1.46504904176263</v>
+        <v>28.75077117637345</v>
       </c>
       <c r="E36" t="n">
         <v>10.06007302342196</v>
@@ -17100,13 +17100,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.3075601374349394</v>
+        <v>0.3690639520539877</v>
       </c>
       <c r="C37" t="n">
-        <v>0.2923645782687812</v>
+        <v>0.2824318289669617</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.589671501258037</v>
+        <v>-14.13602875626897</v>
       </c>
       <c r="E37" t="n">
         <v>5.019525917730211</v>
@@ -17119,13 +17119,13 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6281863640383205</v>
+        <v>0.4911072746275915</v>
       </c>
       <c r="C38" t="n">
-        <v>0.6270745174272765</v>
+        <v>0.6489918454027498</v>
       </c>
       <c r="D38" t="n">
-        <v>2.129795750278479</v>
+        <v>9.302325581395349</v>
       </c>
       <c r="E38" t="n">
         <v>0.8552799899809196</v>
@@ -17138,13 +17138,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7243180306398437</v>
+        <v>0.8662833462695909</v>
       </c>
       <c r="C39" t="n">
-        <v>0.6608645087621836</v>
+        <v>0.6628784021492333</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.061104942260151</v>
+        <v>-7.777048834956708</v>
       </c>
       <c r="E39" t="n">
         <v>0.6612679139637218</v>
@@ -17305,16 +17305,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>14.4655219875708</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1607565011820331</v>
+        <v>0.09085516235841293</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1150793650793651</v>
+        <v>0.07999227521484251</v>
       </c>
       <c r="E12" t="n">
-        <v>0.08768971332209106</v>
+        <v>0.05674805154551658</v>
       </c>
     </row>
     <row r="13">
@@ -17324,16 +17324,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>-5.176224844901513</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9456264775413712</v>
+        <v>0.9701209413341854</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1488095238095238</v>
+        <v>0.1306078444515401</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.06239460370994941</v>
+        <v>0.06465852235017502</v>
       </c>
     </row>
     <row r="14">
@@ -17343,16 +17343,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>-6.82528779814816</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.1394799054373523</v>
+        <v>-0.2561507361364258</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9841269841269841</v>
+        <v>0.5651212014487808</v>
       </c>
       <c r="E14" t="n">
-        <v>0.06239460370994941</v>
+        <v>0.1942581606358842</v>
       </c>
     </row>
     <row r="15">
@@ -17362,16 +17362,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>-1.464009344521129</v>
       </c>
       <c r="C15" t="n">
-        <v>0.03309692671394799</v>
+        <v>0.1951746324438274</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2797619047619048</v>
+        <v>0.2242786788848367</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9123102866779089</v>
+        <v>0.6843352654684242</v>
       </c>
     </row>
     <row r="17">
@@ -17515,16 +17515,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>14.4655219875708</v>
       </c>
       <c r="C28" t="n">
-        <v>0.3886037111280847</v>
+        <v>0.21962815194419</v>
       </c>
       <c r="D28" t="n">
-        <v>-2.301189670129633</v>
+        <v>1.59956910856792</v>
       </c>
       <c r="E28" t="n">
-        <v>19.11346923453935</v>
+        <v>12.36920610461199</v>
       </c>
     </row>
     <row r="29">
@@ -17534,16 +17534,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>-6.341497528393964</v>
       </c>
       <c r="C29" t="n">
-        <v>0.9456264775413712</v>
+        <v>0.9701209413341854</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.3764544692239202</v>
+        <v>0.3304083334237381</v>
       </c>
       <c r="E29" t="n">
-        <v>-4.103594587518039</v>
+        <v>4.25248894257794</v>
       </c>
     </row>
     <row r="30">
@@ -17553,16 +17553,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>-13.644009445377</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.2174167476002595</v>
+        <v>-0.3992794501227125</v>
       </c>
       <c r="D30" t="n">
-        <v>0.9841269841269841</v>
+        <v>0.5651212014487808</v>
       </c>
       <c r="E30" t="n">
-        <v>0.2548410571945653</v>
+        <v>0.7934172521593625</v>
       </c>
     </row>
     <row r="31">
@@ -17572,16 +17572,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>-6.114249864391436</v>
       </c>
       <c r="C31" t="n">
-        <v>0.09854445223723846</v>
+        <v>0.5811227553244643</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4800164597981177</v>
+        <v>0.3848181457662063</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9123102866779089</v>
+        <v>0.6843352654684242</v>
       </c>
     </row>
     <row r="33">
@@ -17844,16 +17844,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.100456621004566</v>
+        <v>0.7762588727408015</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.1743820577858741</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>0.05111615050467857</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>0.05478373802076695</v>
       </c>
     </row>
     <row r="13">
@@ -17863,16 +17863,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06621004566210045</v>
+        <v>0.1225598999257708</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0.7278475182392721</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>0.1421666452330091</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>0.0744141914510891</v>
       </c>
     </row>
     <row r="14">
@@ -17882,16 +17882,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.1027397260273973</v>
+        <v>-0.01995099902903339</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.1093853943601693</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0.5809900497917324</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>0.2004935584515368</v>
       </c>
     </row>
     <row r="15">
@@ -17901,16 +17901,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.0639269406392694</v>
+        <v>0.1211322263624612</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>-0.01161497038531538</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>0.2257271544705801</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0.6703085120766071</v>
       </c>
     </row>
     <row r="17">
@@ -18054,16 +18054,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.100456621004566</v>
+        <v>0.7762588727408015</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.3945856783239448</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>0.9686209939579565</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>13.29088826223352</v>
       </c>
     </row>
     <row r="29">
@@ -18073,16 +18073,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.08542604521321956</v>
+        <v>0.1581301968257005</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>0.7278475182392721</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>0.3630351462970569</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>5.646846075357894</v>
       </c>
     </row>
     <row r="30">
@@ -18092,16 +18092,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.2106541935252711</v>
+        <v>-0.04090687967538243</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.1667631150858042</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0.5809900497917324</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>0.7972340382782119</v>
       </c>
     </row>
     <row r="31">
@@ -18111,16 +18111,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.2752159540549449</v>
+        <v>0.5214940823347577</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>-0.03430575622030282</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>0.3935219279664389</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0.6703085120766071</v>
       </c>
     </row>
     <row r="33">
@@ -18383,16 +18383,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>3.170731707317073</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>-5.641665438105066</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>0.0251300560660283</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>0.04469670235872584</v>
       </c>
     </row>
     <row r="13">
@@ -18402,16 +18402,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>-1.524390243902439</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>4.356019281715876</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>0.1640405211610416</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>0.07358051446374624</v>
       </c>
     </row>
     <row r="14">
@@ -18421,16 +18421,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>-0.6463414634146342</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1.017783987598229</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0.5152555963287407</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>0.2369202884185443</v>
       </c>
     </row>
     <row r="15">
@@ -18443,13 +18443,13 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1.267862168790961</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>0.2955738264441895</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0.6448024947589834</v>
       </c>
     </row>
     <row r="17">
@@ -18488,7 +18488,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2572187581728843</v>
+        <v>0.2522802047317328</v>
       </c>
       <c r="C20" t="n">
         <v>-21.26666666666667</v>
@@ -18507,7 +18507,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.3397329173662127</v>
+        <v>0.3380584711685742</v>
       </c>
       <c r="C21" t="n">
         <v>13.93333333333333</v>
@@ -18526,7 +18526,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2439920367747748</v>
+        <v>0.249141043678863</v>
       </c>
       <c r="C22" t="n">
         <v>3.4</v>
@@ -18545,7 +18545,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.159056287686128</v>
+        <v>0.1605202804208299</v>
       </c>
       <c r="C23" t="n">
         <v>4.933333333333334</v>
@@ -18593,16 +18593,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>3.170731707317073</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>-13.95122123725674</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>0.5239726658742273</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>6.341691393758259</v>
       </c>
     </row>
     <row r="29">
@@ -18612,16 +18612,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>-1.96311755744993</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>4.356019281715876</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>0.4360136542278594</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>3.335199307887255</v>
       </c>
     </row>
     <row r="30">
@@ -18631,16 +18631,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>-1.373736165511932</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>1.600097548863094</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0.5152555963287407</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>0.8979504231989183</v>
       </c>
     </row>
     <row r="31">
@@ -18653,13 +18653,13 @@
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>3.976280766826491</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>0.5333470783179683</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0.6448024947589834</v>
       </c>
     </row>
     <row r="33">
@@ -18698,7 +18698,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.2572187581728843</v>
+        <v>0.2522802047317328</v>
       </c>
       <c r="C36" t="n">
         <v>-52.59013936588819</v>
@@ -18717,7 +18717,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.4375097896309958</v>
+        <v>0.4353534292483851</v>
       </c>
       <c r="C37" t="n">
         <v>13.93333333333333</v>
@@ -18736,7 +18736,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.51858143719213</v>
+        <v>0.5295251525515744</v>
       </c>
       <c r="C38" t="n">
         <v>5.345271425396108</v>
@@ -18755,7 +18755,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7374031970094889</v>
+        <v>0.7441904352801203</v>
       </c>
       <c r="C39" t="n">
         <v>15.47196448678925</v>
@@ -18922,16 +18922,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.118279569892473</v>
+        <v>0.5677949771030327</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.05761230027132949</v>
+        <v>0.04194629986182941</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.01774722130706941</v>
+        <v>0.05168627544602618</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>0.04932429869082544</v>
       </c>
     </row>
     <row r="13">
@@ -18941,16 +18941,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.260752688172043</v>
+        <v>0.1556502011547646</v>
       </c>
       <c r="C13" t="n">
-        <v>1.832107325896895</v>
+        <v>1.212741215965113</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1504901365793322</v>
+        <v>0.1389078843549303</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>0.07160477294029077</v>
       </c>
     </row>
     <row r="14">
@@ -18960,16 +18960,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.01881720430107527</v>
+        <v>0.08655654377627492</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.6610189930660235</v>
+        <v>-0.2034032621553158</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8903752897181136</v>
+        <v>0.5519795175981685</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>0.2103638330411908</v>
       </c>
     </row>
     <row r="15">
@@ -18979,16 +18979,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.3978494623655914</v>
+        <v>0.1899982779659278</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.1134760325595418</v>
+        <v>-0.0512842536716269</v>
       </c>
       <c r="D15" t="n">
-        <v>0.277862068168288</v>
+        <v>0.2574263226008751</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0.6687070953276932</v>
       </c>
     </row>
     <row r="17">
@@ -19132,16 +19132,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.118279569892473</v>
+        <v>0.5677949771030327</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.1416894340770866</v>
+        <v>0.1031610864530619</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.3775444172403431</v>
+        <v>1.099544790982049</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>10.224739247652</v>
       </c>
     </row>
     <row r="29">
@@ -19151,16 +19151,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.3212511601287214</v>
+        <v>0.191763344975548</v>
       </c>
       <c r="C29" t="n">
-        <v>1.832107325896895</v>
+        <v>1.212741215965113</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.3760961294211393</v>
+        <v>0.3471504434739369</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>4.741066115223767</v>
       </c>
     </row>
     <row r="30">
@@ -19170,16 +19170,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.03653976309191945</v>
+        <v>0.1680778692220348</v>
       </c>
       <c r="C30" t="n">
-        <v>-1.009392895401523</v>
+        <v>-0.3106019794813404</v>
       </c>
       <c r="D30" t="n">
-        <v>0.8903752897181136</v>
+        <v>0.5519795175981685</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>0.7827729824532987</v>
       </c>
     </row>
     <row r="31">
@@ -19189,16 +19189,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-1.656796164806828</v>
+        <v>0.7912249431785984</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.3384599633016377</v>
+        <v>-0.1529632841767095</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4981161441564236</v>
+        <v>0.46148151154138</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0.6687070953276932</v>
       </c>
     </row>
     <row r="33">
@@ -19461,16 +19461,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>0.5389457120377655</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.5766636207896952</v>
       </c>
       <c r="D12" t="n">
-        <v>0.05929919137466307</v>
+        <v>0.02528820560052462</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>0.03503641039476203</v>
       </c>
     </row>
     <row r="13">
@@ -19480,16 +19480,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.4024390243902439</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>5.191013973821997</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.2183288409703504</v>
+        <v>0.1516800311751112</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>0.05864152624093042</v>
       </c>
     </row>
     <row r="14">
@@ -19499,16 +19499,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.07867820613690008</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>-4.546854270636506</v>
       </c>
       <c r="D14" t="n">
-        <v>1.199460916442048</v>
+        <v>0.5211967555421226</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>0.2478919559352227</v>
       </c>
     </row>
     <row r="15">
@@ -19518,16 +19518,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>-0.02006294256490952</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>-0.2208233239751864</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.04043126684636118</v>
+        <v>0.3018350076822414</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0.6584301074290849</v>
       </c>
     </row>
     <row r="17">
@@ -19566,13 +19566,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.3430782282571486</v>
+        <v>0.3399624197716013</v>
       </c>
       <c r="C20" t="n">
         <v>0.1810944797714099</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0504779359673998</v>
+        <v>0.0512701298916988</v>
       </c>
       <c r="E20" t="n">
         <v>0.04416159096864049</v>
@@ -19585,13 +19585,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2865565998941029</v>
+        <v>0.2866268285061029</v>
       </c>
       <c r="C21" t="n">
         <v>0.3857968518676188</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1771392102854356</v>
+        <v>0.1785235639469937</v>
       </c>
       <c r="E21" t="n">
         <v>0.067636949358827</v>
@@ -19604,13 +19604,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2182793997502433</v>
+        <v>0.2196391511952639</v>
       </c>
       <c r="C22" t="n">
         <v>0.2692113401080611</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4680798829837187</v>
+        <v>0.4650259094153366</v>
       </c>
       <c r="E22" t="n">
         <v>0.250779539963889</v>
@@ -19623,13 +19623,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1520857720985052</v>
+        <v>0.153771600527032</v>
       </c>
       <c r="C23" t="n">
         <v>0.1638973282529102</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3043029707634462</v>
+        <v>0.3051803967459712</v>
       </c>
       <c r="E23" t="n">
         <v>0.6374219197086437</v>
@@ -19671,16 +19671,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>0.5389457120377655</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>1.397878812773873</v>
       </c>
       <c r="D28" t="n">
-        <v>1.221021122253563</v>
+        <v>0.520705805025943</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>5.996901478840328</v>
       </c>
     </row>
     <row r="29">
@@ -19690,16 +19690,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.5188278702330951</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>5.191013973821997</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5763546345907049</v>
+        <v>0.400412004910107</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>2.846088721003785</v>
       </c>
     </row>
     <row r="30">
@@ -19709,16 +19709,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>0.1694390800148719</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>-7.300536702147884</v>
       </c>
       <c r="D30" t="n">
-        <v>1.199460916442048</v>
+        <v>0.5211967555421226</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>0.8560957897804642</v>
       </c>
     </row>
     <row r="31">
@@ -19728,16 +19728,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>-0.09024538920688722</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>-0.6818187530988871</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.07151793636648444</v>
+        <v>0.5339089906488717</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0.6584301074290849</v>
       </c>
     </row>
     <row r="33">
@@ -19776,13 +19776,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.3430782282571486</v>
+        <v>0.3399624197716013</v>
       </c>
       <c r="C36" t="n">
         <v>0.4389875262741462</v>
       </c>
       <c r="D36" t="n">
-        <v>1.039383920676746</v>
+        <v>1.055695871852918</v>
       </c>
       <c r="E36" t="n">
         <v>7.558785480700227</v>
@@ -19795,13 +19795,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.3694312465088532</v>
+        <v>0.3695217858427276</v>
       </c>
       <c r="C37" t="n">
         <v>0.3857968518676188</v>
       </c>
       <c r="D37" t="n">
-        <v>0.4676203306992915</v>
+        <v>0.4712748119176477</v>
       </c>
       <c r="E37" t="n">
         <v>3.28266965464655</v>
@@ -19814,13 +19814,13 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4700801212412708</v>
+        <v>0.4730084421220531</v>
       </c>
       <c r="C38" t="n">
         <v>0.432252091690237</v>
       </c>
       <c r="D38" t="n">
-        <v>0.4680798829837187</v>
+        <v>0.4650259094153366</v>
       </c>
       <c r="E38" t="n">
         <v>0.8660680719396499</v>
@@ -19833,13 +19833,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6840990373897057</v>
+        <v>0.6916820847007478</v>
       </c>
       <c r="C39" t="n">
         <v>0.506052847923778</v>
       </c>
       <c r="D39" t="n">
-        <v>0.5382745136800234</v>
+        <v>0.5398265722841473</v>
       </c>
       <c r="E39" t="n">
         <v>0.6374219197086437</v>
@@ -20000,16 +20000,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>2.712871287128713</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>0.01479565936697754</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>0.03973010443705073</v>
       </c>
     </row>
     <row r="13">
@@ -20019,16 +20019,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>-0.3069306930693069</v>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>0.131110260261006</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>0.06257099040913137</v>
       </c>
     </row>
     <row r="14">
@@ -20038,16 +20038,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>-1.544554455445545</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0.5468725879860367</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>0.2441602844427318</v>
       </c>
     </row>
     <row r="15">
@@ -20057,16 +20057,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>0.1386138613861386</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>0.3072214923859797</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0.6535386207110857</v>
       </c>
     </row>
     <row r="17">
@@ -20105,13 +20105,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.3217356503010156</v>
+        <v>0.321422136956276</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1874342922606441</v>
+        <v>0.1878119557686526</v>
       </c>
       <c r="D20" t="n">
-        <v>0.04711129440350271</v>
+        <v>0.04654693102105363</v>
       </c>
       <c r="E20" t="n">
         <v>0.04711647322326693</v>
@@ -20124,13 +20124,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2915393943827068</v>
+        <v>0.2913265489867949</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3782887549424021</v>
+        <v>0.3747820812703255</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1627277711016699</v>
+        <v>0.1624616301638967</v>
       </c>
       <c r="E21" t="n">
         <v>0.06943666102750612</v>
@@ -20143,13 +20143,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2259117435998214</v>
+        <v>0.2262570798380048</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2686848293338357</v>
+        <v>0.2707385742030959</v>
       </c>
       <c r="D22" t="n">
-        <v>0.488799538781013</v>
+        <v>0.4893913486523046</v>
       </c>
       <c r="E22" t="n">
         <v>0.245118806185394</v>
@@ -20162,13 +20162,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.160813211716456</v>
+        <v>0.1609942342189242</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1655921234631178</v>
+        <v>0.1666673887579257</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3013613957138147</v>
+        <v>0.3016000901627452</v>
       </c>
       <c r="E23" t="n">
         <v>0.6383280595638327</v>
@@ -20210,16 +20210,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>2.712871287128713</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>0.2927151579499832</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>6.38914800265891</v>
       </c>
     </row>
     <row r="29">
@@ -20229,16 +20229,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>-0.3805608666326366</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>0.3648261299415119</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>3.163211881635496</v>
       </c>
     </row>
     <row r="30">
@@ -20248,16 +20248,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>-3.203639505955122</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0.5468725879860367</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>0.8925485778749993</v>
       </c>
     </row>
     <row r="31">
@@ -20267,16 +20267,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.6111420073037852</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>0.5461093919663923</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0.6535386207110857</v>
       </c>
     </row>
     <row r="33">
@@ -20315,13 +20315,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.3217356503010156</v>
+        <v>0.321422136956276</v>
       </c>
       <c r="C36" t="n">
-        <v>0.4365450759472652</v>
+        <v>0.4374246756341614</v>
       </c>
       <c r="D36" t="n">
-        <v>0.9320429485777294</v>
+        <v>0.9208776660757901</v>
       </c>
       <c r="E36" t="n">
         <v>7.576977837139419</v>
@@ -20334,13 +20334,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.361477320740888</v>
+        <v>0.3612134154679517</v>
       </c>
       <c r="C37" t="n">
-        <v>0.3782887549424021</v>
+        <v>0.3747820812703255</v>
       </c>
       <c r="D37" t="n">
-        <v>0.452804706869208</v>
+        <v>0.452064145694564</v>
       </c>
       <c r="E37" t="n">
         <v>3.510298778189867</v>
@@ -20353,13 +20353,13 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4685751182834281</v>
+        <v>0.4692913978626826</v>
       </c>
       <c r="C38" t="n">
-        <v>0.4230654401112053</v>
+        <v>0.4262992232732242</v>
       </c>
       <c r="D38" t="n">
-        <v>0.488799538781013</v>
+        <v>0.4893913486523046</v>
       </c>
       <c r="E38" t="n">
         <v>0.8960525352046199</v>
@@ -20372,13 +20372,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7090179007104082</v>
+        <v>0.7098160204252711</v>
       </c>
       <c r="C39" t="n">
-        <v>0.5100244941821572</v>
+        <v>0.5133363161856849</v>
       </c>
       <c r="D39" t="n">
-        <v>0.53569262780824</v>
+        <v>0.5361169252080047</v>
       </c>
       <c r="E39" t="n">
         <v>0.6383280595638327</v>
@@ -20545,10 +20545,10 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>0.3828733739576667</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>0.04143091277241286</v>
       </c>
     </row>
     <row r="13">
@@ -20564,10 +20564,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>-0.6791825780775702</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>0.06190857175060661</v>
       </c>
     </row>
     <row r="14">
@@ -20583,10 +20583,10 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>2.355752662379204</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>0.2364492032803507</v>
       </c>
     </row>
     <row r="15">
@@ -20602,10 +20602,10 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>-1.059443458259301</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0.6602113121966299</v>
       </c>
     </row>
     <row r="17">
@@ -20644,16 +20644,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.3373086723354863</v>
+        <v>0.2580788110473752</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1119165852184204</v>
+        <v>0.1042316993752006</v>
       </c>
       <c r="D20" t="n">
         <v>22.5</v>
       </c>
       <c r="E20" t="n">
-        <v>0.05115476825778127</v>
+        <v>0.04382912552549106</v>
       </c>
     </row>
     <row r="21">
@@ -20663,16 +20663,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2895074964850161</v>
+        <v>0.2360946370081433</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2774761045295089</v>
+        <v>0.2748127708045341</v>
       </c>
       <c r="D21" t="n">
         <v>-52</v>
       </c>
       <c r="E21" t="n">
-        <v>0.07841792647099231</v>
+        <v>0.07341954335067472</v>
       </c>
     </row>
     <row r="22">
@@ -20682,16 +20682,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2095130355134156</v>
+        <v>0.3366780698423866</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3723340959610461</v>
+        <v>0.3788818598176603</v>
       </c>
       <c r="D22" t="n">
         <v>115</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2521310817808182</v>
+        <v>0.2524711013463888</v>
       </c>
     </row>
     <row r="23">
@@ -20701,16 +20701,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1636707956660823</v>
+        <v>0.1691484821020952</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2382732142910242</v>
+        <v>0.242073670002605</v>
       </c>
       <c r="D23" t="n">
         <v>-84.5</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6182962234904081</v>
+        <v>0.6302802297774457</v>
       </c>
     </row>
     <row r="25">
@@ -20755,10 +20755,10 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>7.451719911024988</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>6.905441472419897</v>
       </c>
     </row>
     <row r="29">
@@ -20774,10 +20774,10 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>-1.779272066317269</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>3.284234670725926</v>
       </c>
     </row>
     <row r="30">
@@ -20793,10 +20793,10 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>2.355752662379204</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>0.8599579482243112</v>
       </c>
     </row>
     <row r="31">
@@ -20812,10 +20812,10 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>-1.810837955452599</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0.6602113121966299</v>
       </c>
     </row>
     <row r="33">
@@ -20854,16 +20854,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.3373086723354863</v>
+        <v>0.2580788110473752</v>
       </c>
       <c r="C36" t="n">
-        <v>0.2607221165642903</v>
+        <v>0.2428193213826031</v>
       </c>
       <c r="D36" t="n">
         <v>437.9090043921424</v>
       </c>
       <c r="E36" t="n">
-        <v>8.52615196241884</v>
+        <v>7.305160346482927</v>
       </c>
     </row>
     <row r="37">
@@ -20873,16 +20873,16 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.3670676216277352</v>
+        <v>0.2993452602707578</v>
       </c>
       <c r="C37" t="n">
-        <v>0.2774761045295089</v>
+        <v>0.2748127708045341</v>
       </c>
       <c r="D37" t="n">
         <v>-136.2257372831653</v>
       </c>
       <c r="E37" t="n">
-        <v>4.160051922372864</v>
+        <v>3.894888913808424</v>
       </c>
     </row>
     <row r="38">
@@ -20892,16 +20892,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4414759261987699</v>
+        <v>0.7094320520451067</v>
       </c>
       <c r="C38" t="n">
-        <v>0.5996022078164366</v>
+        <v>0.6101466454794791</v>
       </c>
       <c r="D38" t="n">
         <v>115</v>
       </c>
       <c r="E38" t="n">
-        <v>0.9169924227434548</v>
+        <v>0.9182290626809451</v>
       </c>
     </row>
     <row r="39">
@@ -20911,16 +20911,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6758771805959779</v>
+        <v>0.6984972408791479</v>
       </c>
       <c r="C39" t="n">
-        <v>0.7173717379017356</v>
+        <v>0.7288138109301596</v>
       </c>
       <c r="D39" t="n">
         <v>-144.4303667579904</v>
       </c>
       <c r="E39" t="n">
-        <v>0.6182962234904081</v>
+        <v>0.6302802297774457</v>
       </c>
     </row>
   </sheetData>
@@ -21078,16 +21078,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.866831302614591</v>
+        <v>1.532690560660731</v>
       </c>
       <c r="C12" t="n">
-        <v>2.316505260587252</v>
+        <v>1.299029185514235</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>0.149360402503588</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.004208016267498504</v>
+        <v>0.03222092189453904</v>
       </c>
     </row>
     <row r="13">
@@ -21097,16 +21097,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1510630423976731</v>
+        <v>0.2333360239034627</v>
       </c>
       <c r="C13" t="n">
-        <v>2.604025349942853</v>
+        <v>1.412816986320859</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>0.08096849224163297</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.00705013275058165</v>
+        <v>0.03650570317931147</v>
       </c>
     </row>
     <row r="14">
@@ -21116,16 +21116,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.8410757271379098</v>
+        <v>-0.5827205781975028</v>
       </c>
       <c r="C14" t="n">
-        <v>-1.827135052532258</v>
+        <v>-0.8482440386423921</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0.566401699527678</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2037001046312594</v>
+        <v>0.2134780042570971</v>
       </c>
     </row>
     <row r="15">
@@ -21135,16 +21135,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.1768186178743547</v>
+        <v>-0.1833060063666909</v>
       </c>
       <c r="C15" t="n">
-        <v>-2.093395557997847</v>
+        <v>-0.8636021331927012</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>0.2032694057271013</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8075580443868207</v>
+        <v>0.7177953706690523</v>
       </c>
     </row>
     <row r="17">
@@ -21186,13 +21186,13 @@
         <v>0.3646547870108066</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2023849419160474</v>
+        <v>0.196564845080895</v>
       </c>
       <c r="D20" t="n">
-        <v>0.05195989390156671</v>
+        <v>0.05074206219363894</v>
       </c>
       <c r="E20" t="n">
-        <v>0.03140688626641346</v>
+        <v>0.03098561548864065</v>
       </c>
     </row>
     <row r="21">
@@ -21205,13 +21205,13 @@
         <v>0.2849535077355124</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3816411442122545</v>
+        <v>0.3682964628409849</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1643966543271408</v>
+        <v>0.1633696266509497</v>
       </c>
       <c r="E21" t="n">
-        <v>0.03610343648835854</v>
+        <v>0.03534251677643381</v>
       </c>
     </row>
     <row r="22">
@@ -21224,13 +21224,13 @@
         <v>0.1678182370085833</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2642496415858482</v>
+        <v>0.2782851285649699</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4755963759844363</v>
+        <v>0.4766997297996634</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2139561163893944</v>
+        <v>0.2138756062740985</v>
       </c>
     </row>
     <row r="23">
@@ -21243,13 +21243,13 @@
         <v>0.1825734682450974</v>
       </c>
       <c r="C23" t="n">
-        <v>0.15172427228585</v>
+        <v>0.1568535635131507</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3080470757868561</v>
+        <v>0.3091885813557478</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7185335608558334</v>
+        <v>0.7197962614608269</v>
       </c>
     </row>
     <row r="25">
@@ -21288,16 +21288,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.866831302614591</v>
+        <v>1.532690560660731</v>
       </c>
       <c r="C28" t="n">
-        <v>4.929912493044236</v>
+        <v>2.764552414127569</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>1.543170958803033</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.5911328900047484</v>
+        <v>4.526324393099061</v>
       </c>
     </row>
     <row r="29">
@@ -21307,16 +21307,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.2063935715423547</v>
+        <v>0.3188010421248456</v>
       </c>
       <c r="C29" t="n">
-        <v>2.604025349942853</v>
+        <v>1.412816986320859</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>0.1802483215036171</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.372109506590727</v>
+        <v>1.926789136939359</v>
       </c>
     </row>
     <row r="30">
@@ -21326,16 +21326,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-1.84025384562514</v>
+        <v>-1.274978875685741</v>
       </c>
       <c r="C30" t="n">
-        <v>-2.783236847892676</v>
+        <v>-1.29211251302023</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0.566401699527678</v>
       </c>
       <c r="E30" t="n">
-        <v>0.7720420699099331</v>
+        <v>0.8091012058400224</v>
       </c>
     </row>
     <row r="31">
@@ -21345,16 +21345,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.7982318615023183</v>
+        <v>-0.8275185975642755</v>
       </c>
       <c r="C31" t="n">
-        <v>-6.109749721243883</v>
+        <v>-2.520494931013489</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>0.3557014458457677</v>
       </c>
       <c r="E31" t="n">
-        <v>0.8075580443868207</v>
+        <v>0.7177953706690523</v>
       </c>
     </row>
     <row r="33">
@@ -21396,13 +21396,13 @@
         <v>0.3646547870108066</v>
       </c>
       <c r="C36" t="n">
-        <v>0.4307091680435119</v>
+        <v>0.4183230238863984</v>
       </c>
       <c r="D36" t="n">
-        <v>0.5368424157096016</v>
+        <v>0.5242599474457088</v>
       </c>
       <c r="E36" t="n">
-        <v>4.411970454608523</v>
+        <v>4.35279126030198</v>
       </c>
     </row>
     <row r="37">
@@ -21415,13 +21415,13 @@
         <v>0.389324690219269</v>
       </c>
       <c r="C37" t="n">
-        <v>0.3816411442122545</v>
+        <v>0.3682964628409849</v>
       </c>
       <c r="D37" t="n">
-        <v>0.3659722465233332</v>
+        <v>0.3636859248981416</v>
       </c>
       <c r="E37" t="n">
-        <v>1.905557301286898</v>
+        <v>1.865395581135443</v>
       </c>
     </row>
     <row r="38">
@@ -21434,13 +21434,13 @@
         <v>0.3671823428693938</v>
       </c>
       <c r="C38" t="n">
-        <v>0.402525986508149</v>
+        <v>0.4239059520910268</v>
       </c>
       <c r="D38" t="n">
-        <v>0.4755963759844363</v>
+        <v>0.4766997297996634</v>
       </c>
       <c r="E38" t="n">
-        <v>0.8109132946503647</v>
+        <v>0.8106081539329641</v>
       </c>
     </row>
     <row r="39">
@@ -21453,13 +21453,13 @@
         <v>0.8242116196258067</v>
       </c>
       <c r="C39" t="n">
-        <v>0.4428199566788975</v>
+        <v>0.4577902213889993</v>
       </c>
       <c r="D39" t="n">
-        <v>0.539052051901269</v>
+        <v>0.5410495742526695</v>
       </c>
       <c r="E39" t="n">
-        <v>0.7185335608558334</v>
+        <v>0.7197962614608269</v>
       </c>
     </row>
   </sheetData>
@@ -21617,16 +21617,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>1.188811188811189</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>-1.399145299145299</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>-0.03997265684506243</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.4248704663212435</v>
+        <v>0.03269717574761922</v>
       </c>
     </row>
     <row r="13">
@@ -21636,16 +21636,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>-0.1538461538461539</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>2.695940170940171</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>0.1008330037813133</v>
       </c>
       <c r="E13" t="n">
-        <v>0.116580310880829</v>
+        <v>0.0540238651463803</v>
       </c>
     </row>
     <row r="14">
@@ -21655,16 +21655,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>-0.2587412587412588</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.9008295625942685</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0.6265087871011205</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2124352331606218</v>
+        <v>0.1984322486601814</v>
       </c>
     </row>
     <row r="15">
@@ -21674,16 +21674,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>0.2237762237762238</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>-1.19762443438914</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>0.3126308659626287</v>
       </c>
       <c r="E15" t="n">
-        <v>1.095854922279793</v>
+        <v>0.7148467104458188</v>
       </c>
     </row>
     <row r="17">
@@ -21722,16 +21722,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.3514511378479716</v>
+        <v>0.3445582997752294</v>
       </c>
       <c r="C20" t="n">
         <v>0.1863185505644586</v>
       </c>
       <c r="D20" t="n">
-        <v>0.03562144806190252</v>
+        <v>0.03045612672910948</v>
       </c>
       <c r="E20" t="n">
-        <v>0.04467196399682311</v>
+        <v>0.04525981075767908</v>
       </c>
     </row>
     <row r="21">
@@ -21741,16 +21741,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2742223188037922</v>
+        <v>0.2721234405745186</v>
       </c>
       <c r="C21" t="n">
         <v>0.3711447210398913</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1665434981350855</v>
+        <v>0.1650263619419014</v>
       </c>
       <c r="E21" t="n">
-        <v>0.05621584663088874</v>
+        <v>0.05771877178198341</v>
       </c>
     </row>
     <row r="22">
@@ -21760,16 +21760,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2204172118925348</v>
+        <v>0.2251006008088982</v>
       </c>
       <c r="C22" t="n">
         <v>0.2706825939024282</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5026077183305044</v>
+        <v>0.5077220778669078</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2027449717177421</v>
+        <v>0.2052768459725744</v>
       </c>
     </row>
     <row r="23">
@@ -21779,16 +21779,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1539093314557015</v>
+        <v>0.1582176588413539</v>
       </c>
       <c r="C23" t="n">
         <v>0.1718541344932217</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2952273354725074</v>
+        <v>0.2967954334620814</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6963672176545455</v>
+        <v>0.6917445714877626</v>
       </c>
     </row>
     <row r="25">
@@ -21827,16 +21827,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>1.188811188811189</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>-3.123722968610791</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>-0.4148428034746582</v>
       </c>
       <c r="E28" t="n">
-        <v>-57.59990574340428</v>
+        <v>4.432772787069628</v>
       </c>
     </row>
     <row r="29">
@@ -21846,16 +21846,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>-0.2096132231669293</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>2.695940170940171</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>0.2145893596966836</v>
       </c>
       <c r="E29" t="n">
-        <v>6.358371381196246</v>
+        <v>2.946499245481401</v>
       </c>
     </row>
     <row r="30">
@@ -21865,16 +21865,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>-0.5585648188531395</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>1.3497082529582</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0.6265087871011205</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9242556245964295</v>
+        <v>0.8633319397955993</v>
       </c>
     </row>
     <row r="31">
@@ -21884,16 +21884,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>1.037237277618462</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>-3.574409628287377</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>0.5498039829262452</v>
       </c>
       <c r="E31" t="n">
-        <v>1.095854922279793</v>
+        <v>0.7148467104458188</v>
       </c>
     </row>
     <row r="33">
@@ -21932,16 +21932,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.3514511378479716</v>
+        <v>0.3445582997752294</v>
       </c>
       <c r="C36" t="n">
         <v>0.4159736206325416</v>
       </c>
       <c r="D36" t="n">
-        <v>0.3696852434679214</v>
+        <v>0.316078689596634</v>
       </c>
       <c r="E36" t="n">
-        <v>6.056200935473461</v>
+        <v>6.135895620561945</v>
       </c>
     </row>
     <row r="37">
@@ -21951,16 +21951,16 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.3736240567070188</v>
+        <v>0.3707643646076447</v>
       </c>
       <c r="C37" t="n">
         <v>0.3711447210398913</v>
       </c>
       <c r="D37" t="n">
-        <v>0.3544321926971789</v>
+        <v>0.3512034751933929</v>
       </c>
       <c r="E37" t="n">
-        <v>3.066051442879962</v>
+        <v>3.14802202776345</v>
       </c>
     </row>
     <row r="38">
@@ -21970,16 +21970,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4758317271540564</v>
+        <v>0.4859421219724695</v>
       </c>
       <c r="C38" t="n">
         <v>0.4055623239873508</v>
       </c>
       <c r="D38" t="n">
-        <v>0.5026077183305044</v>
+        <v>0.5077220778669078</v>
       </c>
       <c r="E38" t="n">
-        <v>0.8820955812310259</v>
+        <v>0.8931111693045461</v>
       </c>
     </row>
     <row r="39">
@@ -21989,16 +21989,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7133934663176275</v>
+        <v>0.7333632275959833</v>
       </c>
       <c r="C39" t="n">
         <v>0.5129129427848418</v>
       </c>
       <c r="D39" t="n">
-        <v>0.5191975028175574</v>
+        <v>0.5219552168315968</v>
       </c>
       <c r="E39" t="n">
-        <v>0.6963672176545455</v>
+        <v>0.6917445714877626</v>
       </c>
     </row>
   </sheetData>

--- a/results/excel/srd_all_matrices.xlsx
+++ b/results/excel/srd_all_matrices.xlsx
@@ -4134,10 +4134,10 @@
         <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>0.4146452413256463</v>
+        <v>0.4146452413256462</v>
       </c>
       <c r="D36" t="n">
-        <v>476.666499407698</v>
+        <v>476.6664994076979</v>
       </c>
       <c r="E36" t="n">
         <v>1.908119289362967</v>
@@ -21579,7 +21579,7 @@
         <v>1.646492035973749</v>
       </c>
       <c r="C39" t="n">
-        <v>0.6561264159158579</v>
+        <v>0.656126415915858</v>
       </c>
       <c r="D39" t="n">
         <v>0.3562330767014248</v>
